--- a/model/Outputs/11. Interest rate/10/Output Files/0.1/Output_18_41.xlsx
+++ b/model/Outputs/11. Interest rate/10/Output Files/0.1/Output_18_41.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4187629.696459008</v>
+        <v>4187726.1282138</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16358981.96022835</v>
+        <v>16358981.96022836</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16358981.96022835</v>
+        <v>16358981.96022836</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3260900.580844234</v>
+        <v>3260900.580844235</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3260900.580844234</v>
+        <v>3260900.580844235</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>46717730.22967867</v>
+        <v>46717730.22967866</v>
       </c>
     </row>
   </sheetData>
@@ -663,7 +663,7 @@
         <v>6.339155739849787</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3632896068686478</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0.8896287080118555</v>
@@ -705,25 +705,25 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>75.82444920935808</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>139.5400751442118</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="V2" t="n">
-        <v>107.6838020638948</v>
+        <v>184</v>
       </c>
       <c r="W2" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>107.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -745,16 +745,16 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>169.8864182944728</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,16 +778,16 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>128.0504349018003</v>
       </c>
       <c r="R3" t="n">
         <v>121.3720614433227</v>
       </c>
       <c r="S3" t="n">
-        <v>184</v>
+        <v>56.01173581366788</v>
       </c>
       <c r="T3" t="n">
-        <v>169.948589009941</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>121.9291408454554</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>184</v>
@@ -860,7 +860,7 @@
         <v>184</v>
       </c>
       <c r="R4" t="n">
-        <v>40.13805915454443</v>
+        <v>162.0671999999999</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>74.82444920935808</v>
       </c>
       <c r="T5" t="n">
-        <v>111.2890339403184</v>
+        <v>178.7895113768051</v>
       </c>
       <c r="U5" t="n">
         <v>244.1685528300177</v>
@@ -954,7 +954,7 @@
         <v>224.8510241668239</v>
       </c>
       <c r="W5" t="n">
-        <v>233.3734759809475</v>
+        <v>91.04854933510293</v>
       </c>
       <c r="X5" t="n">
         <v>187.2818334606677</v>
@@ -979,10 +979,10 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>228.3478504532637</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>318</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1015,19 +1015,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>128.0504349018003</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>120.3720614433227</v>
+        <v>318</v>
       </c>
       <c r="S6" t="n">
-        <v>297.9253541081407</v>
+        <v>318</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>318</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>9.510667191520156</v>
@@ -1039,7 +1039,7 @@
         <v>14.86273944538755</v>
       </c>
       <c r="Y6" t="n">
-        <v>318</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1082,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>69.27338189435318</v>
+        <v>68.46115743886361</v>
       </c>
       <c r="N7" t="n">
         <v>120.9291408454554</v>
@@ -1097,7 +1097,7 @@
         <v>296.075266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>307.4924609027107</v>
+        <v>308.3046853582002</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1131,7 +1131,7 @@
         <v>76.99931295557451</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>44.47457824299391</v>
       </c>
       <c r="D8" t="n">
         <v>5.339155739849787</v>
@@ -1179,19 +1179,19 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>74.82444920935808</v>
       </c>
       <c r="T8" t="n">
         <v>178.7895113768051</v>
       </c>
       <c r="U8" t="n">
-        <v>221.1426536365248</v>
+        <v>244.1685528300177</v>
       </c>
       <c r="V8" t="n">
         <v>224.8510241668239</v>
       </c>
       <c r="W8" t="n">
-        <v>233.3734759809475</v>
+        <v>91.04854933510293</v>
       </c>
       <c r="X8" t="n">
         <v>187.2818334606677</v>
@@ -1207,16 +1207,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>318</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>52.96405319627313</v>
       </c>
       <c r="E9" t="n">
-        <v>318</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>128.0504349018003</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>120.3720614433227</v>
@@ -1273,10 +1273,10 @@
         <v>27.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>257.7763577398604</v>
+        <v>14.86273944538755</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>173.9993129555745</v>
       </c>
       <c r="C11" t="n">
         <v>141.4745782429939</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>102.3391557398498</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>95.09807580460415</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1422,19 +1422,19 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>326.0000000000119</v>
       </c>
       <c r="V11" t="n">
-        <v>310.0669556135244</v>
+        <v>141.9478437962979</v>
       </c>
       <c r="W11" t="n">
-        <v>326.0000000000074</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>284.2818334606677</v>
       </c>
       <c r="Y11" t="n">
-        <v>203.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1459,10 +1459,10 @@
         <v>31.63624233787687</v>
       </c>
       <c r="G12" t="n">
-        <v>16.83227724499633</v>
+        <v>17.38678115804621</v>
       </c>
       <c r="H12" t="n">
-        <v>20.76121926189283</v>
+        <v>20.20671534882764</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.553189576952718e-11</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>217.3720614433227</v>
@@ -1553,28 +1553,28 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>71.57949701023819</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>217.9291408454554</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>274.4125840807951</v>
+        <v>290.6443837511461</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>326.0000000000214</v>
       </c>
       <c r="Q13" t="n">
         <v>326</v>
       </c>
       <c r="R13" t="n">
-        <v>326</v>
+        <v>322.4964162488325</v>
       </c>
       <c r="S13" t="n">
-        <v>49.21957806351117</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1602,13 +1602,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>173.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>141.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>102.3391557398498</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1617,10 +1617,10 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>95.09807580460415</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>93.2576386030249</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1662,16 +1662,16 @@
         <v>326.0000000000018</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>321.8510241668239</v>
       </c>
       <c r="W14" t="n">
-        <v>326.0000000000018</v>
+        <v>123.2774730028889</v>
       </c>
       <c r="X14" t="n">
-        <v>284.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>13.38507534076017</v>
+        <v>203.3174326828064</v>
       </c>
     </row>
     <row r="15">
@@ -1696,10 +1696,10 @@
         <v>31.63624233787687</v>
       </c>
       <c r="G15" t="n">
-        <v>17.38678115804623</v>
+        <v>17.38678115804621</v>
       </c>
       <c r="H15" t="n">
-        <v>20.76121926189285</v>
+        <v>20.20671534882764</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1729,7 +1729,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>216.8175575302574</v>
+        <v>217.3720614433227</v>
       </c>
       <c r="S15" t="n">
         <v>152.0117358136679</v>
@@ -1805,13 +1805,13 @@
         <v>326</v>
       </c>
       <c r="Q16" t="n">
-        <v>322.4964162488538</v>
+        <v>273.2768381853426</v>
       </c>
       <c r="R16" t="n">
         <v>326</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>49.21957806351117</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1890,10 +1890,10 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>75.82444920935808</v>
       </c>
       <c r="T17" t="n">
-        <v>133.082515625438</v>
+        <v>179.7895113768051</v>
       </c>
       <c r="U17" t="n">
         <v>245.1685528300177</v>
@@ -1905,7 +1905,7 @@
         <v>234.3734759809475</v>
       </c>
       <c r="X17" t="n">
-        <v>188.2818334606677</v>
+        <v>65.75038849994246</v>
       </c>
       <c r="Y17" t="n">
         <v>107.3174326828064</v>
@@ -1918,25 +1918,25 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>83.99681494805525</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
         <v>326</v>
       </c>
-      <c r="C18" t="n">
-        <v>326</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>325.3867811580462</v>
       </c>
       <c r="H18" t="n">
-        <v>55.01045319627287</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1981,13 +1981,13 @@
         <v>10.51066719152016</v>
       </c>
       <c r="W18" t="n">
-        <v>28.37314290982852</v>
+        <v>326</v>
       </c>
       <c r="X18" t="n">
         <v>15.86273944538755</v>
       </c>
       <c r="Y18" t="n">
-        <v>326</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>78.99931295557451</v>
+        <v>72.43619219024596</v>
       </c>
       <c r="C20" t="n">
         <v>46.47457824299391</v>
@@ -2145,7 +2145,7 @@
         <v>189.2818334606677</v>
       </c>
       <c r="Y20" t="n">
-        <v>101.7543119174778</v>
+        <v>108.3174326828064</v>
       </c>
     </row>
     <row r="21">
@@ -2164,16 +2164,16 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>170.8443332892392</v>
       </c>
       <c r="H21" t="n">
-        <v>7.837051680291685</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2200,13 +2200,13 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>128.0504349018003</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>122.3720614433227</v>
       </c>
       <c r="S21" t="n">
-        <v>57.01173581366788</v>
+        <v>359.0000000000024</v>
       </c>
       <c r="T21" t="n">
         <v>0.9359161609100397</v>
@@ -2215,13 +2215,13 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>359.0000000000024</v>
+        <v>11.51066719152016</v>
       </c>
       <c r="W21" t="n">
-        <v>359.0000000000024</v>
+        <v>29.37314290982852</v>
       </c>
       <c r="X21" t="n">
-        <v>359.0000000000024</v>
+        <v>16.86273944538755</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -2364,13 +2364,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>74.24020424863296</v>
+        <v>76.82444920935808</v>
       </c>
       <c r="T23" t="n">
         <v>180.7895113768051</v>
       </c>
       <c r="U23" t="n">
-        <v>246.1685528300177</v>
+        <v>243.5843078692925</v>
       </c>
       <c r="V23" t="n">
         <v>226.8510241668239</v>
@@ -2395,13 +2395,13 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>357.646834077814</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2413,7 +2413,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>204.9811028724806</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>128.0504349018003</v>
+        <v>48.35381722623388</v>
       </c>
       <c r="R24" t="n">
-        <v>122.3720614433227</v>
+        <v>360.0000000000124</v>
       </c>
       <c r="S24" t="n">
         <v>57.01173581366788</v>
@@ -2553,22 +2553,22 @@
         <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>142.4745782429939</v>
       </c>
       <c r="D26" t="n">
-        <v>93.49554315036953</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>97.36328960686865</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>97.88962870801186</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>94.2576386030249</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2601,25 +2601,25 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>172.8244492093581</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>276.7895113768051</v>
       </c>
       <c r="U26" t="n">
-        <v>330</v>
+        <v>76.21388008611359</v>
       </c>
       <c r="V26" t="n">
         <v>322.8510241668239</v>
       </c>
       <c r="W26" t="n">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>204.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2644,10 +2644,10 @@
         <v>32.63624233787687</v>
       </c>
       <c r="G27" t="n">
-        <v>18.35547724498085</v>
+        <v>18.38678115804621</v>
       </c>
       <c r="H27" t="n">
-        <v>21.76121926189283</v>
+        <v>21.72991534882747</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2747,19 +2747,19 @@
         <v>218.9291408454554</v>
       </c>
       <c r="O28" t="n">
-        <v>291.6443837511461</v>
+        <v>139.6215040606929</v>
       </c>
       <c r="P28" t="n">
-        <v>127.7575422460848</v>
+        <v>330.0000000000245</v>
       </c>
       <c r="Q28" t="n">
-        <v>330</v>
+        <v>330.0000000000248</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>50.21957806351117</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2793,7 +2793,7 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>65.33915573984979</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -2841,22 +2841,22 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>196.0000000000003</v>
       </c>
       <c r="U29" t="n">
-        <v>172.6368</v>
+        <v>196.0000000000003</v>
       </c>
       <c r="V29" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>196</v>
+        <v>136.9802115773433</v>
       </c>
       <c r="X29" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>166.3174326828064</v>
       </c>
     </row>
     <row r="30">
@@ -2984,19 +2984,19 @@
         <v>180.9291408454554</v>
       </c>
       <c r="O31" t="n">
-        <v>187.7076591545446</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>196</v>
+        <v>175.4880810910329</v>
       </c>
       <c r="Q31" t="n">
-        <v>196</v>
+        <v>196.0000000000003</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>196.0000000000003</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>12.21957806351118</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3109,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>196.0000000000004</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -3148,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>128.0504349018003</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>49.37206144332269</v>
@@ -3160,19 +3160,19 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>196.0000000000004</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>123.2647385566761</v>
       </c>
       <c r="W33" t="n">
-        <v>191.2143036548769</v>
+        <v>196.0000000000004</v>
       </c>
       <c r="X33" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -3227,10 +3227,10 @@
         <v>175.6797661807365</v>
       </c>
       <c r="Q34" t="n">
-        <v>196</v>
+        <v>196.0000000000004</v>
       </c>
       <c r="R34" t="n">
-        <v>196</v>
+        <v>196.0000000000004</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3340,7 +3340,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>180.1679036548769</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -3349,10 +3349,10 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>120.2183385566772</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>128.0504349018003</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>45.37206144332269</v>
@@ -3400,7 +3400,7 @@
         <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
         <v>0</v>
@@ -3409,7 +3409,7 @@
         <v>188</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
     </row>
     <row r="37">
@@ -3580,19 +3580,19 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>120.2183385566772</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>180.1679036548769</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -3622,10 +3622,10 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>128.0504349018003</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>45.37206144332269</v>
+        <v>45.37206144332265</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -3692,7 +3692,7 @@
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>45.92914084545539</v>
+        <v>45.92914084545544</v>
       </c>
       <c r="O40" t="n">
         <v>118.6443837511461</v>
@@ -3741,19 +3741,19 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>137.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>131.3632896068686</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>131.8896287080119</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>128.2576386030249</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3786,22 +3786,22 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>28.25124426015011</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>188</v>
+        <v>150.0798430820945</v>
       </c>
       <c r="X41" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -3814,19 +3814,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>111.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
         <v>88.09991244551929</v>
       </c>
       <c r="D42" t="n">
-        <v>74.93768689770263</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>69.67209722191262</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>66.63624233787687</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>52.38678115804623</v>
@@ -3868,19 +3868,19 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>118.5776877314996</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>141.5106671915202</v>
       </c>
       <c r="W42" t="n">
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>84.14851126458855</v>
+        <v>146.8627394453875</v>
       </c>
       <c r="Y42" t="n">
         <v>126.3913927661343</v>
@@ -3893,19 +3893,19 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>14.11380033707866</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>12.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>7.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1.382855967741932</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -3923,13 +3923,13 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>106.5794970102382</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>118.1535464291398</v>
+        <v>188</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>111.5077352411185</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -3944,7 +3944,7 @@
         <v>188</v>
       </c>
       <c r="S43" t="n">
-        <v>84.21957806351116</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3962,7 +3962,7 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>14.46535284946236</v>
       </c>
     </row>
     <row r="44">
@@ -4023,7 +4023,7 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
         <v>155</v>
@@ -4038,7 +4038,7 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -4063,13 +4063,13 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>104.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>90.38678115804623</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>93.76121926189285</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4108,19 +4108,19 @@
         <v>155</v>
       </c>
       <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
         <v>155</v>
       </c>
-      <c r="V45" t="n">
-        <v>2.739757242183981</v>
-      </c>
       <c r="W45" t="n">
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>136.5239999999999</v>
       </c>
     </row>
     <row r="46">
@@ -4130,13 +4130,13 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>52.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>50.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -4157,16 +4157,16 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>19.16142953884798</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>144.5794970102382</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -4178,10 +4178,10 @@
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>81.69686101516098</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>122.2195780635112</v>
+        <v>66.1700974192709</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -4196,10 +4196,10 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>12.44364543010755</v>
       </c>
       <c r="Y46" t="n">
-        <v>52.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4297,13 +4297,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>68.32267908861031</v>
+        <v>67.95571988975308</v>
       </c>
       <c r="C2" t="n">
-        <v>22.38876167144474</v>
+        <v>22.02180247258752</v>
       </c>
       <c r="D2" t="n">
-        <v>15.98557405543485</v>
+        <v>15.61861485657763</v>
       </c>
       <c r="E2" t="n">
         <v>15.61861485657763</v>
@@ -4321,25 +4321,25 @@
         <v>14.72</v>
       </c>
       <c r="J2" t="n">
-        <v>196.88</v>
+        <v>35.42481899323997</v>
       </c>
       <c r="K2" t="n">
-        <v>279.9063350753769</v>
+        <v>118.4511540686169</v>
       </c>
       <c r="L2" t="n">
-        <v>382.9078454271357</v>
+        <v>300.6111540686168</v>
       </c>
       <c r="M2" t="n">
-        <v>382.9078454271357</v>
+        <v>482.7711540686169</v>
       </c>
       <c r="N2" t="n">
-        <v>419.8367988110885</v>
+        <v>482.7711540686169</v>
       </c>
       <c r="O2" t="n">
-        <v>460.2646077317319</v>
+        <v>553.84</v>
       </c>
       <c r="P2" t="n">
-        <v>553.84</v>
+        <v>736</v>
       </c>
       <c r="Q2" t="n">
         <v>736</v>
@@ -4348,25 +4348,25 @@
         <v>736</v>
       </c>
       <c r="S2" t="n">
-        <v>736</v>
+        <v>659.4096472632747</v>
       </c>
       <c r="T2" t="n">
-        <v>736</v>
+        <v>518.4600764105355</v>
       </c>
       <c r="U2" t="n">
-        <v>736</v>
+        <v>332.6014905519496</v>
       </c>
       <c r="V2" t="n">
-        <v>627.2284827637426</v>
+        <v>146.7429046933637</v>
       </c>
       <c r="W2" t="n">
-        <v>441.3698969051567</v>
+        <v>146.7429046933637</v>
       </c>
       <c r="X2" t="n">
-        <v>255.5113110465708</v>
+        <v>146.7429046933637</v>
       </c>
       <c r="Y2" t="n">
-        <v>147.1098638922209</v>
+        <v>146.7429046933637</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>200.5785858585859</v>
+        <v>372.1810285802756</v>
       </c>
       <c r="C3" t="n">
-        <v>200.5785858585859</v>
+        <v>372.1810285802756</v>
       </c>
       <c r="D3" t="n">
-        <v>200.5785858585859</v>
+        <v>372.1810285802756</v>
       </c>
       <c r="E3" t="n">
-        <v>200.5785858585859</v>
+        <v>372.1810285802756</v>
       </c>
       <c r="F3" t="n">
         <v>200.5785858585859</v>
       </c>
       <c r="G3" t="n">
-        <v>200.5785858585859</v>
+        <v>14.72</v>
       </c>
       <c r="H3" t="n">
-        <v>200.5785858585859</v>
+        <v>14.72</v>
       </c>
       <c r="I3" t="n">
         <v>14.72</v>
       </c>
       <c r="J3" t="n">
-        <v>171.6708292319027</v>
+        <v>14.72</v>
       </c>
       <c r="K3" t="n">
-        <v>353.8308292319027</v>
+        <v>14.72</v>
       </c>
       <c r="L3" t="n">
-        <v>535.9908292319027</v>
+        <v>196.88</v>
       </c>
       <c r="M3" t="n">
-        <v>556.7835830776631</v>
+        <v>371.4467417428592</v>
       </c>
       <c r="N3" t="n">
-        <v>556.7835830776631</v>
+        <v>553.6067417428592</v>
       </c>
       <c r="O3" t="n">
-        <v>556.7835830776631</v>
+        <v>735.7667417428592</v>
       </c>
       <c r="P3" t="n">
         <v>736</v>
       </c>
       <c r="Q3" t="n">
-        <v>736</v>
+        <v>606.6561263618178</v>
       </c>
       <c r="R3" t="n">
-        <v>613.4019581380579</v>
+        <v>484.0580844998757</v>
       </c>
       <c r="S3" t="n">
-        <v>427.543372279472</v>
+        <v>427.4805735769788</v>
       </c>
       <c r="T3" t="n">
-        <v>255.8781308552891</v>
+        <v>427.4805735769788</v>
       </c>
       <c r="U3" t="n">
-        <v>255.8781308552891</v>
+        <v>427.4805735769788</v>
       </c>
       <c r="V3" t="n">
-        <v>245.2612953082991</v>
+        <v>416.8637380299888</v>
       </c>
       <c r="W3" t="n">
-        <v>216.601554995341</v>
+        <v>388.2039977170307</v>
       </c>
       <c r="X3" t="n">
-        <v>200.5785858585859</v>
+        <v>372.1810285802756</v>
       </c>
       <c r="Y3" t="n">
-        <v>200.5785858585859</v>
+        <v>372.1810285802756</v>
       </c>
     </row>
     <row r="4">
@@ -4455,34 +4455,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>391.8743270009949</v>
+        <v>199.1635172835954</v>
       </c>
       <c r="C4" t="n">
-        <v>391.8743270009949</v>
+        <v>199.1635172835954</v>
       </c>
       <c r="D4" t="n">
-        <v>391.8743270009949</v>
+        <v>199.1635172835954</v>
       </c>
       <c r="E4" t="n">
-        <v>391.8743270009949</v>
+        <v>199.1635172835954</v>
       </c>
       <c r="F4" t="n">
-        <v>391.8743270009949</v>
+        <v>199.1635172835954</v>
       </c>
       <c r="G4" t="n">
-        <v>391.8743270009949</v>
+        <v>199.1635172835954</v>
       </c>
       <c r="H4" t="n">
-        <v>567.9539954390809</v>
+        <v>199.1635172835954</v>
       </c>
       <c r="I4" t="n">
-        <v>567.9539954390809</v>
+        <v>381.3235172835954</v>
       </c>
       <c r="J4" t="n">
-        <v>567.9539954390809</v>
+        <v>563.4835172835953</v>
       </c>
       <c r="K4" t="n">
-        <v>716.2941801956215</v>
+        <v>711.8237020401358</v>
       </c>
       <c r="L4" t="n">
         <v>736</v>
@@ -4491,40 +4491,40 @@
         <v>736</v>
       </c>
       <c r="N4" t="n">
-        <v>612.8392516712571</v>
+        <v>736</v>
       </c>
       <c r="O4" t="n">
-        <v>426.9806658126712</v>
+        <v>550.1414141414141</v>
       </c>
       <c r="P4" t="n">
-        <v>241.1220799540853</v>
+        <v>364.2828282828282</v>
       </c>
       <c r="Q4" t="n">
-        <v>55.26349409549942</v>
+        <v>178.4242424242423</v>
       </c>
       <c r="R4" t="n">
         <v>14.72</v>
       </c>
       <c r="S4" t="n">
-        <v>61.03261771712395</v>
+        <v>14.72</v>
       </c>
       <c r="T4" t="n">
-        <v>61.03261771712395</v>
+        <v>14.72</v>
       </c>
       <c r="U4" t="n">
-        <v>61.03261771712395</v>
+        <v>14.72</v>
       </c>
       <c r="V4" t="n">
-        <v>61.03261771712395</v>
+        <v>14.72</v>
       </c>
       <c r="W4" t="n">
-        <v>236.8835359768013</v>
+        <v>14.72</v>
       </c>
       <c r="X4" t="n">
-        <v>391.8743270009949</v>
+        <v>169.7107910241935</v>
       </c>
       <c r="Y4" t="n">
-        <v>391.8743270009949</v>
+        <v>199.1635172835954</v>
       </c>
     </row>
     <row r="5">
@@ -4561,13 +4561,13 @@
         <v>340.26</v>
       </c>
       <c r="K5" t="n">
-        <v>423.2863350753768</v>
+        <v>508.3567988110885</v>
       </c>
       <c r="L5" t="n">
-        <v>526.2878454271356</v>
+        <v>823.1767988110885</v>
       </c>
       <c r="M5" t="n">
-        <v>841.1078454271355</v>
+        <v>1137.996798811088</v>
       </c>
       <c r="N5" t="n">
         <v>1137.996798811088</v>
@@ -4585,16 +4585,16 @@
         <v>1272</v>
       </c>
       <c r="S5" t="n">
-        <v>1272</v>
+        <v>1196.419748273376</v>
       </c>
       <c r="T5" t="n">
-        <v>1159.586834403719</v>
+        <v>1015.824282236199</v>
       </c>
       <c r="U5" t="n">
-        <v>912.951932555216</v>
+        <v>769.1893803876961</v>
       </c>
       <c r="V5" t="n">
-        <v>685.8296859220605</v>
+        <v>542.0671337545407</v>
       </c>
       <c r="W5" t="n">
         <v>450.0989021029216</v>
@@ -4613,16 +4613,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25.44</v>
+        <v>577.3065156093573</v>
       </c>
       <c r="C6" t="n">
-        <v>25.44</v>
+        <v>577.3065156093573</v>
       </c>
       <c r="D6" t="n">
-        <v>25.44</v>
+        <v>577.3065156093573</v>
       </c>
       <c r="E6" t="n">
-        <v>25.44</v>
+        <v>346.6521212121212</v>
       </c>
       <c r="F6" t="n">
         <v>25.44</v>
@@ -4649,40 +4649,40 @@
         <v>917.3629165031076</v>
       </c>
       <c r="N6" t="n">
-        <v>1141.47136752577</v>
+        <v>1092.783583077663</v>
       </c>
       <c r="O6" t="n">
-        <v>1141.47136752577</v>
+        <v>1092.783583077663</v>
       </c>
       <c r="P6" t="n">
         <v>1272</v>
       </c>
       <c r="Q6" t="n">
-        <v>1142.656126361818</v>
+        <v>1272</v>
       </c>
       <c r="R6" t="n">
-        <v>1021.068185509977</v>
+        <v>950.7878787878788</v>
       </c>
       <c r="S6" t="n">
-        <v>720.1334843906427</v>
+        <v>629.5757575757575</v>
       </c>
       <c r="T6" t="n">
-        <v>720.1334843906427</v>
+        <v>629.5757575757575</v>
       </c>
       <c r="U6" t="n">
-        <v>398.9213631785215</v>
+        <v>629.5757575757575</v>
       </c>
       <c r="V6" t="n">
-        <v>389.3146286416325</v>
+        <v>619.9690230388685</v>
       </c>
       <c r="W6" t="n">
-        <v>361.6649893387753</v>
+        <v>592.3193837360114</v>
       </c>
       <c r="X6" t="n">
-        <v>346.6521212121212</v>
+        <v>577.3065156093573</v>
       </c>
       <c r="Y6" t="n">
-        <v>25.44</v>
+        <v>577.3065156093573</v>
       </c>
     </row>
     <row r="7">
@@ -4692,76 +4692,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>395.9449149254168</v>
+        <v>851.8461232705837</v>
       </c>
       <c r="C7" t="n">
-        <v>526.8969207438525</v>
+        <v>982.7981290890194</v>
       </c>
       <c r="D7" t="n">
-        <v>526.8969207438525</v>
+        <v>982.7981290890194</v>
       </c>
       <c r="E7" t="n">
-        <v>526.8969207438525</v>
+        <v>1105.577033300433</v>
       </c>
       <c r="F7" t="n">
-        <v>526.8969207438525</v>
+        <v>1105.577033300433</v>
       </c>
       <c r="G7" t="n">
-        <v>685.5462669586067</v>
+        <v>1105.577033300433</v>
       </c>
       <c r="H7" t="n">
-        <v>862.6159353966927</v>
+        <v>1105.577033300433</v>
       </c>
       <c r="I7" t="n">
-        <v>1097.503517283595</v>
+        <v>1105.577033300433</v>
       </c>
       <c r="J7" t="n">
-        <v>1097.503517283595</v>
+        <v>1272</v>
       </c>
       <c r="K7" t="n">
-        <v>1246.833702040136</v>
+        <v>1272</v>
       </c>
       <c r="L7" t="n">
         <v>1272</v>
       </c>
       <c r="M7" t="n">
-        <v>1202.026886975401</v>
+        <v>1202.84731571832</v>
       </c>
       <c r="N7" t="n">
-        <v>1079.876239656759</v>
+        <v>1080.696668399678</v>
       </c>
       <c r="O7" t="n">
-        <v>884.2758520293387</v>
+        <v>885.0962807722574</v>
       </c>
       <c r="P7" t="n">
-        <v>635.1043710386957</v>
+        <v>635.9247997816144</v>
       </c>
       <c r="Q7" t="n">
-        <v>336.0384453562735</v>
+        <v>336.8588740991922</v>
       </c>
       <c r="R7" t="n">
         <v>25.44</v>
       </c>
       <c r="S7" t="n">
-        <v>72.74261771712393</v>
+        <v>25.44</v>
       </c>
       <c r="T7" t="n">
-        <v>267.0192673677321</v>
+        <v>219.7166496506081</v>
       </c>
       <c r="U7" t="n">
-        <v>279.2375772591247</v>
+        <v>471.2338121249603</v>
       </c>
       <c r="V7" t="n">
-        <v>279.2375772591247</v>
+        <v>675.0052050109063</v>
       </c>
       <c r="W7" t="n">
-        <v>279.2375772591247</v>
+        <v>851.8461232705837</v>
       </c>
       <c r="X7" t="n">
-        <v>279.2375772591247</v>
+        <v>851.8461232705837</v>
       </c>
       <c r="Y7" t="n">
-        <v>279.2375772591247</v>
+        <v>851.8461232705837</v>
       </c>
     </row>
     <row r="8">
@@ -4771,7 +4771,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30.83308660590893</v>
+        <v>75.7569030129735</v>
       </c>
       <c r="C8" t="n">
         <v>30.83308660590893</v>
@@ -4795,25 +4795,25 @@
         <v>25.44</v>
       </c>
       <c r="J8" t="n">
-        <v>322.3289533839528</v>
+        <v>46.14481899323998</v>
       </c>
       <c r="K8" t="n">
-        <v>405.3552884593297</v>
+        <v>129.1711540686169</v>
       </c>
       <c r="L8" t="n">
-        <v>508.3567988110885</v>
+        <v>233.964607731732</v>
       </c>
       <c r="M8" t="n">
-        <v>823.1767988110885</v>
+        <v>233.964607731732</v>
       </c>
       <c r="N8" t="n">
-        <v>1137.996798811088</v>
+        <v>548.784607731732</v>
       </c>
       <c r="O8" t="n">
-        <v>1178.424607731732</v>
+        <v>863.6046077317319</v>
       </c>
       <c r="P8" t="n">
-        <v>1272</v>
+        <v>957.1800000000001</v>
       </c>
       <c r="Q8" t="n">
         <v>1272</v>
@@ -4822,25 +4822,25 @@
         <v>1272</v>
       </c>
       <c r="S8" t="n">
-        <v>1272</v>
+        <v>1196.419748273376</v>
       </c>
       <c r="T8" t="n">
-        <v>1091.404533962823</v>
+        <v>1015.824282236199</v>
       </c>
       <c r="U8" t="n">
-        <v>868.0281161481515</v>
+        <v>769.1893803876961</v>
       </c>
       <c r="V8" t="n">
-        <v>640.9058695149961</v>
+        <v>542.0671337545407</v>
       </c>
       <c r="W8" t="n">
-        <v>405.1750856958571</v>
+        <v>450.0989021029216</v>
       </c>
       <c r="X8" t="n">
-        <v>216.0015165436674</v>
+        <v>260.925332950732</v>
       </c>
       <c r="Y8" t="n">
-        <v>108.6101703994185</v>
+        <v>153.5339868064831</v>
       </c>
     </row>
     <row r="9">
@@ -4850,13 +4850,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>667.8642424242425</v>
+        <v>400.1511648447204</v>
       </c>
       <c r="C9" t="n">
-        <v>667.8642424242425</v>
+        <v>400.1511648447204</v>
       </c>
       <c r="D9" t="n">
-        <v>667.8642424242425</v>
+        <v>346.6521212121212</v>
       </c>
       <c r="E9" t="n">
         <v>346.6521212121212</v>
@@ -4877,13 +4877,13 @@
         <v>182.3908292319027</v>
       </c>
       <c r="K9" t="n">
-        <v>182.3908292319027</v>
+        <v>427.9761747602484</v>
       </c>
       <c r="L9" t="n">
-        <v>379.2883903121412</v>
+        <v>603.3968413348039</v>
       </c>
       <c r="M9" t="n">
-        <v>553.8551320550005</v>
+        <v>777.9635830776631</v>
       </c>
       <c r="N9" t="n">
         <v>777.9635830776631</v>
@@ -4895,31 +4895,31 @@
         <v>1272</v>
       </c>
       <c r="Q9" t="n">
-        <v>1142.656126361818</v>
+        <v>1272</v>
       </c>
       <c r="R9" t="n">
-        <v>1021.068185509977</v>
+        <v>1150.412059148159</v>
       </c>
       <c r="S9" t="n">
-        <v>965.5007755971809</v>
+        <v>1094.844649235363</v>
       </c>
       <c r="T9" t="n">
-        <v>965.5007755971809</v>
+        <v>1094.844649235363</v>
       </c>
       <c r="U9" t="n">
-        <v>965.5007755971809</v>
+        <v>1094.844649235363</v>
       </c>
       <c r="V9" t="n">
-        <v>955.8940410602919</v>
+        <v>1085.237914698474</v>
       </c>
       <c r="W9" t="n">
-        <v>928.2444017574348</v>
+        <v>1057.588275395617</v>
       </c>
       <c r="X9" t="n">
-        <v>667.8642424242425</v>
+        <v>1042.575407268963</v>
       </c>
       <c r="Y9" t="n">
-        <v>667.8642424242425</v>
+        <v>721.3632860568416</v>
       </c>
     </row>
     <row r="10">
@@ -4929,28 +4929,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>72.74261771712393</v>
+        <v>181.4207910241935</v>
       </c>
       <c r="C10" t="n">
-        <v>156.5378998155039</v>
+        <v>181.4207910241935</v>
       </c>
       <c r="D10" t="n">
-        <v>274.807043940504</v>
+        <v>299.6899351491936</v>
       </c>
       <c r="E10" t="n">
-        <v>397.585948151917</v>
+        <v>422.4688393606066</v>
       </c>
       <c r="F10" t="n">
-        <v>526.8969207438525</v>
+        <v>422.4688393606066</v>
       </c>
       <c r="G10" t="n">
-        <v>685.5462669586067</v>
+        <v>581.1181855753607</v>
       </c>
       <c r="H10" t="n">
-        <v>862.6159353966927</v>
+        <v>581.1181855753607</v>
       </c>
       <c r="I10" t="n">
-        <v>1097.503517283595</v>
+        <v>782.6835172835954</v>
       </c>
       <c r="J10" t="n">
         <v>1097.503517283595</v>
@@ -4980,25 +4980,25 @@
         <v>25.44</v>
       </c>
       <c r="S10" t="n">
-        <v>72.74261771712393</v>
+        <v>25.44</v>
       </c>
       <c r="T10" t="n">
-        <v>72.74261771712393</v>
+        <v>25.44</v>
       </c>
       <c r="U10" t="n">
-        <v>72.74261771712393</v>
+        <v>25.44</v>
       </c>
       <c r="V10" t="n">
-        <v>72.74261771712393</v>
+        <v>25.44</v>
       </c>
       <c r="W10" t="n">
-        <v>72.74261771712393</v>
+        <v>25.44</v>
       </c>
       <c r="X10" t="n">
-        <v>72.74261771712393</v>
+        <v>181.4207910241935</v>
       </c>
       <c r="Y10" t="n">
-        <v>72.74261771712393</v>
+        <v>181.4207910241935</v>
       </c>
     </row>
     <row r="11">
@@ -5008,19 +5008,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>168.9836143868626</v>
+        <v>368.4151614014625</v>
       </c>
       <c r="C11" t="n">
-        <v>26.08</v>
+        <v>225.5115470146</v>
       </c>
       <c r="D11" t="n">
-        <v>26.08</v>
+        <v>122.1386624288931</v>
       </c>
       <c r="E11" t="n">
-        <v>26.08</v>
+        <v>122.1386624288931</v>
       </c>
       <c r="F11" t="n">
-        <v>26.08</v>
+        <v>122.1386624288931</v>
       </c>
       <c r="G11" t="n">
         <v>26.08</v>
@@ -5032,22 +5032,22 @@
         <v>26.08</v>
       </c>
       <c r="J11" t="n">
-        <v>348.82</v>
+        <v>46.78481899323998</v>
       </c>
       <c r="K11" t="n">
-        <v>671.5600000000001</v>
+        <v>129.8111540686169</v>
       </c>
       <c r="L11" t="n">
-        <v>847.2567988110884</v>
+        <v>335.78</v>
       </c>
       <c r="M11" t="n">
-        <v>1169.996798811088</v>
+        <v>335.78</v>
       </c>
       <c r="N11" t="n">
-        <v>1169.996798811088</v>
+        <v>658.52</v>
       </c>
       <c r="O11" t="n">
-        <v>1210.424607731732</v>
+        <v>981.26</v>
       </c>
       <c r="P11" t="n">
         <v>1304</v>
@@ -5065,19 +5065,19 @@
         <v>1304</v>
       </c>
       <c r="U11" t="n">
-        <v>1304</v>
+        <v>974.7070707070586</v>
       </c>
       <c r="V11" t="n">
-        <v>990.8010549358339</v>
+        <v>831.3254103067577</v>
       </c>
       <c r="W11" t="n">
-        <v>661.5081256428971</v>
+        <v>831.3254103067577</v>
       </c>
       <c r="X11" t="n">
-        <v>374.3547585109094</v>
+        <v>544.1720431747701</v>
       </c>
       <c r="Y11" t="n">
-        <v>168.9836143868626</v>
+        <v>544.1720431747701</v>
       </c>
     </row>
     <row r="12">
@@ -5087,22 +5087,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>225.0087226362632</v>
+        <v>225.0087226362477</v>
       </c>
       <c r="C12" t="n">
-        <v>171.372447438769</v>
+        <v>171.3724474387535</v>
       </c>
       <c r="D12" t="n">
-        <v>131.0313495623017</v>
+        <v>131.0313495622862</v>
       </c>
       <c r="E12" t="n">
-        <v>96.00902913612731</v>
+        <v>96.00902913611185</v>
       </c>
       <c r="F12" t="n">
-        <v>64.05322879483754</v>
+        <v>64.05322879482208</v>
       </c>
       <c r="G12" t="n">
-        <v>47.0509285473665</v>
+        <v>46.49082358467439</v>
       </c>
       <c r="H12" t="n">
         <v>26.08</v>
@@ -5114,49 +5114,49 @@
         <v>183.0308292319027</v>
       </c>
       <c r="K12" t="n">
-        <v>428.6161747602484</v>
+        <v>255.8026528241116</v>
       </c>
       <c r="L12" t="n">
-        <v>583.1923280035894</v>
+        <v>578.5426528241117</v>
       </c>
       <c r="M12" t="n">
-        <v>757.7590697464486</v>
+        <v>578.5426528241117</v>
       </c>
       <c r="N12" t="n">
-        <v>981.8675207691113</v>
+        <v>802.6511038467743</v>
       </c>
       <c r="O12" t="n">
-        <v>1304</v>
+        <v>1124.783583077663</v>
       </c>
       <c r="P12" t="n">
         <v>1304</v>
       </c>
       <c r="Q12" t="n">
-        <v>1304.000000000016</v>
+        <v>1304</v>
       </c>
       <c r="R12" t="n">
-        <v>1084.432261168376</v>
+        <v>1084.432261168361</v>
       </c>
       <c r="S12" t="n">
-        <v>930.8850532757826</v>
+        <v>930.8850532757672</v>
       </c>
       <c r="T12" t="n">
-        <v>833.9800874566815</v>
+        <v>833.9800874566661</v>
       </c>
       <c r="U12" t="n">
-        <v>740.8617518879776</v>
+        <v>740.8617518879621</v>
       </c>
       <c r="V12" t="n">
-        <v>633.2752193712905</v>
+        <v>633.2752193712751</v>
       </c>
       <c r="W12" t="n">
-        <v>507.6457820886354</v>
+        <v>507.64578208862</v>
       </c>
       <c r="X12" t="n">
-        <v>394.6531159821834</v>
+        <v>394.6531159821679</v>
       </c>
       <c r="Y12" t="n">
-        <v>302.3385778345729</v>
+        <v>302.3385778345574</v>
       </c>
     </row>
     <row r="13">
@@ -5172,49 +5172,49 @@
         <v>604.2455584585374</v>
       </c>
       <c r="D13" t="n">
-        <v>617.4500320675889</v>
+        <v>626.4847025835375</v>
       </c>
       <c r="E13" t="n">
-        <v>644.1989362790019</v>
+        <v>653.2336067949504</v>
       </c>
       <c r="F13" t="n">
-        <v>677.4799088709374</v>
+        <v>686.5145793868859</v>
       </c>
       <c r="G13" t="n">
-        <v>740.0992550856915</v>
+        <v>749.13392560164</v>
       </c>
       <c r="H13" t="n">
-        <v>821.1389235237776</v>
+        <v>830.1735940397261</v>
       </c>
       <c r="I13" t="n">
-        <v>959.9965054106802</v>
+        <v>969.0311759266287</v>
       </c>
       <c r="J13" t="n">
-        <v>1250.699815243459</v>
+        <v>1259.734485759408</v>
       </c>
       <c r="K13" t="n">
         <v>1304</v>
       </c>
       <c r="L13" t="n">
-        <v>1231.697477767436</v>
+        <v>1304</v>
       </c>
       <c r="M13" t="n">
-        <v>1231.697477767436</v>
+        <v>1304</v>
       </c>
       <c r="N13" t="n">
-        <v>1011.567032468996</v>
+        <v>1304</v>
       </c>
       <c r="O13" t="n">
-        <v>734.3826041045568</v>
+        <v>1010.419814392782</v>
       </c>
       <c r="P13" t="n">
-        <v>734.3826041045568</v>
+        <v>681.1268850998308</v>
       </c>
       <c r="Q13" t="n">
-        <v>405.0896748116275</v>
+        <v>351.8339558069015</v>
       </c>
       <c r="R13" t="n">
-        <v>75.79674551869816</v>
+        <v>26.08</v>
       </c>
       <c r="S13" t="n">
         <v>26.08</v>
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>168.9836143868626</v>
+        <v>319.7111819671504</v>
       </c>
       <c r="C14" t="n">
-        <v>26.08</v>
+        <v>319.7111819671504</v>
       </c>
       <c r="D14" t="n">
-        <v>26.08</v>
+        <v>216.3382973814435</v>
       </c>
       <c r="E14" t="n">
-        <v>26.08</v>
+        <v>216.3382973814435</v>
       </c>
       <c r="F14" t="n">
-        <v>26.08</v>
+        <v>216.3382973814435</v>
       </c>
       <c r="G14" t="n">
-        <v>26.08</v>
+        <v>120.2796349525504</v>
       </c>
       <c r="H14" t="n">
         <v>26.08</v>
@@ -5272,22 +5272,22 @@
         <v>46.78481899323998</v>
       </c>
       <c r="K14" t="n">
-        <v>129.8111540686169</v>
+        <v>369.52481899324</v>
       </c>
       <c r="L14" t="n">
-        <v>232.8126644203757</v>
+        <v>692.2648189932399</v>
       </c>
       <c r="M14" t="n">
-        <v>524.5167988110884</v>
+        <v>1015.00481899324</v>
       </c>
       <c r="N14" t="n">
-        <v>847.2567988110884</v>
+        <v>1015.00481899324</v>
       </c>
       <c r="O14" t="n">
-        <v>887.6846077317318</v>
+        <v>1055.432627913883</v>
       </c>
       <c r="P14" t="n">
-        <v>981.26</v>
+        <v>1304</v>
       </c>
       <c r="Q14" t="n">
         <v>1304</v>
@@ -5305,16 +5305,16 @@
         <v>974.7070707070689</v>
       </c>
       <c r="V14" t="n">
-        <v>974.7070707070689</v>
+        <v>649.6050260941154</v>
       </c>
       <c r="W14" t="n">
-        <v>645.4141414141377</v>
+        <v>525.0823260911973</v>
       </c>
       <c r="X14" t="n">
-        <v>358.2607742821501</v>
+        <v>525.0823260911973</v>
       </c>
       <c r="Y14" t="n">
-        <v>344.7404961601702</v>
+        <v>319.7111819671504</v>
       </c>
     </row>
     <row r="15">
@@ -5324,22 +5324,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>225.5688275989399</v>
+        <v>225.0087226362477</v>
       </c>
       <c r="C15" t="n">
-        <v>171.9325524014457</v>
+        <v>171.3724474387535</v>
       </c>
       <c r="D15" t="n">
-        <v>131.5914545249784</v>
+        <v>131.0313495622862</v>
       </c>
       <c r="E15" t="n">
-        <v>96.569134098804</v>
+        <v>96.00902913611185</v>
       </c>
       <c r="F15" t="n">
-        <v>64.61333375751423</v>
+        <v>64.05322879482208</v>
       </c>
       <c r="G15" t="n">
-        <v>47.05092854736652</v>
+        <v>46.49082358467439</v>
       </c>
       <c r="H15" t="n">
         <v>26.08</v>
@@ -5351,19 +5351,19 @@
         <v>183.0308292319027</v>
       </c>
       <c r="K15" t="n">
-        <v>428.6161747602484</v>
+        <v>305.344362103915</v>
       </c>
       <c r="L15" t="n">
-        <v>751.3561747602485</v>
+        <v>628.0843621039151</v>
       </c>
       <c r="M15" t="n">
-        <v>925.9229165031077</v>
+        <v>802.6511038467743</v>
       </c>
       <c r="N15" t="n">
-        <v>981.8675207691113</v>
+        <v>802.6511038467743</v>
       </c>
       <c r="O15" t="n">
-        <v>1304</v>
+        <v>1124.783583077663</v>
       </c>
       <c r="P15" t="n">
         <v>1304</v>
@@ -5372,28 +5372,28 @@
         <v>1304</v>
       </c>
       <c r="R15" t="n">
-        <v>1084.992366131053</v>
+        <v>1084.432261168361</v>
       </c>
       <c r="S15" t="n">
-        <v>931.4451582384593</v>
+        <v>930.8850532757672</v>
       </c>
       <c r="T15" t="n">
-        <v>834.5401924193582</v>
+        <v>833.9800874566661</v>
       </c>
       <c r="U15" t="n">
-        <v>741.4218568506542</v>
+        <v>740.8617518879621</v>
       </c>
       <c r="V15" t="n">
-        <v>633.8353243339672</v>
+        <v>633.2752193712751</v>
       </c>
       <c r="W15" t="n">
-        <v>508.2058870513121</v>
+        <v>507.64578208862</v>
       </c>
       <c r="X15" t="n">
-        <v>395.21322094486</v>
+        <v>394.6531159821679</v>
       </c>
       <c r="Y15" t="n">
-        <v>302.8986827972496</v>
+        <v>302.3385778345574</v>
       </c>
     </row>
     <row r="16">
@@ -5403,31 +5403,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>560.2888821241531</v>
+        <v>569.3235526401016</v>
       </c>
       <c r="C16" t="n">
-        <v>595.2108879425889</v>
+        <v>604.2455584585374</v>
       </c>
       <c r="D16" t="n">
-        <v>617.4500320675889</v>
+        <v>626.4847025835375</v>
       </c>
       <c r="E16" t="n">
-        <v>644.1989362790019</v>
+        <v>653.2336067949504</v>
       </c>
       <c r="F16" t="n">
-        <v>677.4799088709374</v>
+        <v>686.5145793868859</v>
       </c>
       <c r="G16" t="n">
-        <v>740.0992550856915</v>
+        <v>749.13392560164</v>
       </c>
       <c r="H16" t="n">
-        <v>821.1389235237776</v>
+        <v>830.1735940397261</v>
       </c>
       <c r="I16" t="n">
-        <v>959.9965054106802</v>
+        <v>969.0311759266287</v>
       </c>
       <c r="J16" t="n">
-        <v>1250.699815243459</v>
+        <v>1259.734485759408</v>
       </c>
       <c r="K16" t="n">
         <v>1304</v>
@@ -5448,10 +5448,10 @@
         <v>681.1268850998524</v>
       </c>
       <c r="Q16" t="n">
-        <v>355.3729292929293</v>
+        <v>405.0896748116275</v>
       </c>
       <c r="R16" t="n">
-        <v>26.08</v>
+        <v>75.79674551869816</v>
       </c>
       <c r="S16" t="n">
         <v>26.08</v>
@@ -5460,19 +5460,19 @@
         <v>124.3266496506081</v>
       </c>
       <c r="U16" t="n">
-        <v>270.7791416090118</v>
+        <v>279.8138121249604</v>
       </c>
       <c r="V16" t="n">
-        <v>378.5205344949578</v>
+        <v>387.5552050109063</v>
       </c>
       <c r="W16" t="n">
-        <v>459.3314527546352</v>
+        <v>468.3661232705837</v>
       </c>
       <c r="X16" t="n">
-        <v>519.2822437788287</v>
+        <v>528.3169142947772</v>
       </c>
       <c r="Y16" t="n">
-        <v>539.611544457861</v>
+        <v>548.6462149738095</v>
       </c>
     </row>
     <row r="17">
@@ -5506,25 +5506,25 @@
         <v>26.08</v>
       </c>
       <c r="J17" t="n">
-        <v>348.82</v>
+        <v>201.7767988110885</v>
       </c>
       <c r="K17" t="n">
-        <v>431.8463350753769</v>
+        <v>524.5167988110885</v>
       </c>
       <c r="L17" t="n">
-        <v>534.8478454271357</v>
+        <v>847.2567988110884</v>
       </c>
       <c r="M17" t="n">
         <v>847.2567988110884</v>
       </c>
       <c r="N17" t="n">
-        <v>1169.996798811088</v>
+        <v>847.2567988110884</v>
       </c>
       <c r="O17" t="n">
-        <v>1210.424607731732</v>
+        <v>887.6846077317318</v>
       </c>
       <c r="P17" t="n">
-        <v>1304</v>
+        <v>981.26</v>
       </c>
       <c r="Q17" t="n">
         <v>1304</v>
@@ -5533,19 +5533,19 @@
         <v>1304</v>
       </c>
       <c r="S17" t="n">
-        <v>1304</v>
+        <v>1227.409647263275</v>
       </c>
       <c r="T17" t="n">
-        <v>1169.573216539962</v>
+        <v>1045.804080215997</v>
       </c>
       <c r="U17" t="n">
-        <v>921.9282136813579</v>
+        <v>798.159077357393</v>
       </c>
       <c r="V17" t="n">
-        <v>693.7958660381014</v>
+        <v>570.0267297141365</v>
       </c>
       <c r="W17" t="n">
-        <v>457.0549812088615</v>
+        <v>333.2858448848966</v>
       </c>
       <c r="X17" t="n">
         <v>266.8713110465708</v>
@@ -5561,22 +5561,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>410.9390436325989</v>
+        <v>768.8917132384863</v>
       </c>
       <c r="C18" t="n">
-        <v>81.64611433966957</v>
+        <v>768.8917132384863</v>
       </c>
       <c r="D18" t="n">
-        <v>81.64611433966957</v>
+        <v>684.0464456141881</v>
       </c>
       <c r="E18" t="n">
-        <v>81.64611433966957</v>
+        <v>684.0464456141881</v>
       </c>
       <c r="F18" t="n">
-        <v>81.64611433966957</v>
+        <v>354.7535163212588</v>
       </c>
       <c r="G18" t="n">
-        <v>81.64611433966957</v>
+        <v>26.08</v>
       </c>
       <c r="H18" t="n">
         <v>26.08</v>
@@ -5585,19 +5585,19 @@
         <v>26.08</v>
       </c>
       <c r="J18" t="n">
-        <v>183.0308292319027</v>
+        <v>26.08</v>
       </c>
       <c r="K18" t="n">
-        <v>428.6161747602484</v>
+        <v>81.23591108125242</v>
       </c>
       <c r="L18" t="n">
-        <v>428.6161747602484</v>
+        <v>403.9759110812524</v>
       </c>
       <c r="M18" t="n">
-        <v>603.1829165031077</v>
+        <v>578.5426528241117</v>
       </c>
       <c r="N18" t="n">
-        <v>827.2913675257703</v>
+        <v>802.6511038467743</v>
       </c>
       <c r="O18" t="n">
         <v>1124.783583077663</v>
@@ -5624,13 +5624,13 @@
         <v>1114.207611668171</v>
       </c>
       <c r="W18" t="n">
-        <v>1085.547871355213</v>
+        <v>784.9146823752415</v>
       </c>
       <c r="X18" t="n">
-        <v>1069.524902218458</v>
+        <v>768.8917132384863</v>
       </c>
       <c r="Y18" t="n">
-        <v>740.2319729255282</v>
+        <v>768.8917132384863</v>
       </c>
     </row>
     <row r="19">
@@ -5640,34 +5640,34 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1121.86168858877</v>
+        <v>655.9863933092797</v>
       </c>
       <c r="C19" t="n">
-        <v>1121.86168858877</v>
+        <v>655.9863933092797</v>
       </c>
       <c r="D19" t="n">
-        <v>1121.86168858877</v>
+        <v>773.2655374342797</v>
       </c>
       <c r="E19" t="n">
-        <v>1121.86168858877</v>
+        <v>773.2655374342797</v>
       </c>
       <c r="F19" t="n">
-        <v>1121.86168858877</v>
+        <v>773.2655374342797</v>
       </c>
       <c r="G19" t="n">
-        <v>1279.521034803525</v>
+        <v>930.9248836490339</v>
       </c>
       <c r="H19" t="n">
-        <v>1279.521034803525</v>
+        <v>1107.00455208712</v>
       </c>
       <c r="I19" t="n">
-        <v>1279.521034803525</v>
+        <v>1107.00455208712</v>
       </c>
       <c r="J19" t="n">
-        <v>1279.521034803525</v>
+        <v>1107.00455208712</v>
       </c>
       <c r="K19" t="n">
-        <v>1279.521034803525</v>
+        <v>1255.34473684366</v>
       </c>
       <c r="L19" t="n">
         <v>1279.521034803525</v>
@@ -5691,25 +5691,25 @@
         <v>26.08</v>
       </c>
       <c r="S19" t="n">
-        <v>72.39261771712394</v>
+        <v>26.08</v>
       </c>
       <c r="T19" t="n">
-        <v>265.6792673677321</v>
+        <v>219.3666496506081</v>
       </c>
       <c r="U19" t="n">
-        <v>516.2064298420843</v>
+        <v>469.8938121249604</v>
       </c>
       <c r="V19" t="n">
-        <v>718.9878227280302</v>
+        <v>469.8938121249604</v>
       </c>
       <c r="W19" t="n">
-        <v>890.7750502434461</v>
+        <v>469.8938121249604</v>
       </c>
       <c r="X19" t="n">
-        <v>890.7750502434461</v>
+        <v>469.8938121249604</v>
       </c>
       <c r="Y19" t="n">
-        <v>1006.144350922478</v>
+        <v>585.2631128039926</v>
       </c>
     </row>
     <row r="20">
@@ -5743,25 +5743,25 @@
         <v>28.72</v>
       </c>
       <c r="J20" t="n">
-        <v>49.73895338394561</v>
+        <v>49.42481899323997</v>
       </c>
       <c r="K20" t="n">
-        <v>132.7652884593225</v>
+        <v>404.8348189932399</v>
       </c>
       <c r="L20" t="n">
-        <v>235.7667988110813</v>
+        <v>760.24481899324</v>
       </c>
       <c r="M20" t="n">
-        <v>591.1767988110837</v>
+        <v>760.24481899324</v>
       </c>
       <c r="N20" t="n">
-        <v>946.5867988110861</v>
+        <v>1115.654818993242</v>
       </c>
       <c r="O20" t="n">
-        <v>987.0146077317295</v>
+        <v>1156.082627913885</v>
       </c>
       <c r="P20" t="n">
-        <v>1080.589999999998</v>
+        <v>1436</v>
       </c>
       <c r="Q20" t="n">
         <v>1436</v>
@@ -5788,7 +5788,7 @@
         <v>269.041568662</v>
       </c>
       <c r="Y20" t="n">
-        <v>166.2594354120224</v>
+        <v>159.6300204975491</v>
       </c>
     </row>
     <row r="21">
@@ -5798,22 +5798,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>36.63621381847645</v>
+        <v>890.4903766151805</v>
       </c>
       <c r="C21" t="n">
-        <v>36.63621381847645</v>
+        <v>890.4903766151805</v>
       </c>
       <c r="D21" t="n">
-        <v>36.63621381847645</v>
+        <v>890.4903766151805</v>
       </c>
       <c r="E21" t="n">
-        <v>36.63621381847645</v>
+        <v>544.356945077895</v>
       </c>
       <c r="F21" t="n">
-        <v>36.63621381847645</v>
+        <v>201.2900336254941</v>
       </c>
       <c r="G21" t="n">
-        <v>36.63621381847645</v>
+        <v>28.72</v>
       </c>
       <c r="H21" t="n">
         <v>28.72</v>
@@ -5822,52 +5822,52 @@
         <v>28.72</v>
       </c>
       <c r="J21" t="n">
-        <v>185.6708292319027</v>
+        <v>28.72</v>
       </c>
       <c r="K21" t="n">
-        <v>188.7987343917127</v>
+        <v>274.3053455283457</v>
       </c>
       <c r="L21" t="n">
-        <v>535.9759110812524</v>
+        <v>621.4825222178854</v>
       </c>
       <c r="M21" t="n">
-        <v>710.5426528241117</v>
+        <v>796.0492639607446</v>
       </c>
       <c r="N21" t="n">
-        <v>934.6511038467743</v>
+        <v>1020.157714983407</v>
       </c>
       <c r="O21" t="n">
-        <v>1256.783583077663</v>
+        <v>1342.290194214296</v>
       </c>
       <c r="P21" t="n">
         <v>1436</v>
       </c>
       <c r="Q21" t="n">
-        <v>1306.656126361818</v>
+        <v>1436</v>
       </c>
       <c r="R21" t="n">
-        <v>1183.047983489775</v>
+        <v>1312.391857127957</v>
       </c>
       <c r="S21" t="n">
-        <v>1125.460371556777</v>
+        <v>949.7655945016918</v>
       </c>
       <c r="T21" t="n">
-        <v>1124.515001697272</v>
+        <v>948.8202246421868</v>
       </c>
       <c r="U21" t="n">
-        <v>1124.515001697272</v>
+        <v>948.8202246421868</v>
       </c>
       <c r="V21" t="n">
-        <v>761.8887390710067</v>
+        <v>937.1932880850957</v>
       </c>
       <c r="W21" t="n">
-        <v>399.2624764447416</v>
+        <v>907.5234467620365</v>
       </c>
       <c r="X21" t="n">
-        <v>36.63621381847645</v>
+        <v>890.4903766151805</v>
       </c>
       <c r="Y21" t="n">
-        <v>36.63621381847645</v>
+        <v>890.4903766151805</v>
       </c>
     </row>
     <row r="22">
@@ -5877,22 +5877,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>425.6875890160475</v>
+        <v>728.1082300460691</v>
       </c>
       <c r="C22" t="n">
-        <v>425.6875890160475</v>
+        <v>728.1082300460691</v>
       </c>
       <c r="D22" t="n">
-        <v>425.6875890160475</v>
+        <v>728.1082300460691</v>
       </c>
       <c r="E22" t="n">
-        <v>425.6875890160475</v>
+        <v>728.1082300460691</v>
       </c>
       <c r="F22" t="n">
-        <v>553.018561607983</v>
+        <v>728.1082300460691</v>
       </c>
       <c r="G22" t="n">
-        <v>709.6879078227371</v>
+        <v>884.7775762608233</v>
       </c>
       <c r="H22" t="n">
         <v>884.7775762608233</v>
@@ -5928,25 +5928,25 @@
         <v>28.72</v>
       </c>
       <c r="S22" t="n">
-        <v>74.04261771712395</v>
+        <v>28.72</v>
       </c>
       <c r="T22" t="n">
-        <v>266.3392673677321</v>
+        <v>101.9187564260936</v>
       </c>
       <c r="U22" t="n">
-        <v>425.6875890160475</v>
+        <v>351.4559189004458</v>
       </c>
       <c r="V22" t="n">
-        <v>425.6875890160475</v>
+        <v>553.2473117863917</v>
       </c>
       <c r="W22" t="n">
-        <v>425.6875890160475</v>
+        <v>728.1082300460691</v>
       </c>
       <c r="X22" t="n">
-        <v>425.6875890160475</v>
+        <v>728.1082300460691</v>
       </c>
       <c r="Y22" t="n">
-        <v>425.6875890160475</v>
+        <v>728.1082300460691</v>
       </c>
     </row>
     <row r="23">
@@ -5980,25 +5980,25 @@
         <v>28.8</v>
       </c>
       <c r="J23" t="n">
-        <v>49.50481899323998</v>
+        <v>385.2000000000065</v>
       </c>
       <c r="K23" t="n">
-        <v>405.9048189932399</v>
+        <v>468.2263350753834</v>
       </c>
       <c r="L23" t="n">
-        <v>508.9063293449987</v>
+        <v>571.2278454271421</v>
       </c>
       <c r="M23" t="n">
-        <v>865.3063293449987</v>
+        <v>571.2278454271421</v>
       </c>
       <c r="N23" t="n">
-        <v>949.5967988110883</v>
+        <v>571.2278454271421</v>
       </c>
       <c r="O23" t="n">
-        <v>990.0246077317317</v>
+        <v>727.1999999999871</v>
       </c>
       <c r="P23" t="n">
-        <v>1083.6</v>
+        <v>1083.599999999994</v>
       </c>
       <c r="Q23" t="n">
         <v>1440</v>
@@ -6007,10 +6007,10 @@
         <v>1440</v>
       </c>
       <c r="S23" t="n">
-        <v>1365.009894698351</v>
+        <v>1362.399546253174</v>
       </c>
       <c r="T23" t="n">
-        <v>1182.394226640972</v>
+        <v>1179.783878195795</v>
       </c>
       <c r="U23" t="n">
         <v>933.739122772267</v>
@@ -6035,43 +6035,43 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1070.185153670266</v>
+        <v>910.6585669216561</v>
       </c>
       <c r="C24" t="n">
-        <v>708.9257253088373</v>
+        <v>910.6585669216561</v>
       </c>
       <c r="D24" t="n">
-        <v>357.4735163212588</v>
+        <v>910.6585669216561</v>
       </c>
       <c r="E24" t="n">
-        <v>357.4735163212588</v>
+        <v>564.5251353843706</v>
       </c>
       <c r="F24" t="n">
-        <v>357.4735163212588</v>
+        <v>564.5251353843706</v>
       </c>
       <c r="G24" t="n">
-        <v>28.8</v>
+        <v>235.8516190631118</v>
       </c>
       <c r="H24" t="n">
-        <v>28.8</v>
+        <v>235.8516190631118</v>
       </c>
       <c r="I24" t="n">
         <v>28.8</v>
       </c>
       <c r="J24" t="n">
-        <v>28.8</v>
+        <v>185.7508292319027</v>
       </c>
       <c r="K24" t="n">
-        <v>192.7987343917127</v>
+        <v>431.3361747602484</v>
       </c>
       <c r="L24" t="n">
-        <v>539.9759110812524</v>
+        <v>778.5133514497882</v>
       </c>
       <c r="M24" t="n">
-        <v>714.5426528241117</v>
+        <v>778.5133514497882</v>
       </c>
       <c r="N24" t="n">
-        <v>938.6511038467743</v>
+        <v>1002.621802472451</v>
       </c>
       <c r="O24" t="n">
         <v>1260.783583077663</v>
@@ -6080,31 +6080,31 @@
         <v>1440</v>
       </c>
       <c r="Q24" t="n">
-        <v>1310.656126361818</v>
+        <v>1391.157760377542</v>
       </c>
       <c r="R24" t="n">
-        <v>1187.047983489775</v>
+        <v>1027.521396741165</v>
       </c>
       <c r="S24" t="n">
-        <v>1129.460371556777</v>
+        <v>969.9337848081674</v>
       </c>
       <c r="T24" t="n">
-        <v>1128.515001697272</v>
+        <v>968.9884149486624</v>
       </c>
       <c r="U24" t="n">
-        <v>1128.515001697272</v>
+        <v>968.9884149486624</v>
       </c>
       <c r="V24" t="n">
-        <v>1116.888065140181</v>
+        <v>957.3614783915713</v>
       </c>
       <c r="W24" t="n">
-        <v>1087.218223817122</v>
+        <v>927.6916370685121</v>
       </c>
       <c r="X24" t="n">
-        <v>1070.185153670266</v>
+        <v>910.6585669216561</v>
       </c>
       <c r="Y24" t="n">
-        <v>1070.185153670266</v>
+        <v>910.6585669216561</v>
       </c>
     </row>
     <row r="25">
@@ -6114,31 +6114,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>786.0061434948857</v>
+        <v>579.6498421531106</v>
       </c>
       <c r="C25" t="n">
-        <v>786.0061434948857</v>
+        <v>579.6498421531106</v>
       </c>
       <c r="D25" t="n">
-        <v>786.0061434948857</v>
+        <v>579.6498421531106</v>
       </c>
       <c r="E25" t="n">
-        <v>786.0061434948857</v>
+        <v>700.4487463645237</v>
       </c>
       <c r="F25" t="n">
-        <v>786.0061434948857</v>
+        <v>700.4487463645237</v>
       </c>
       <c r="G25" t="n">
-        <v>942.6754897096398</v>
+        <v>857.1180925792778</v>
       </c>
       <c r="H25" t="n">
-        <v>1117.765158147726</v>
+        <v>1032.207761017364</v>
       </c>
       <c r="I25" t="n">
-        <v>1117.765158147726</v>
+        <v>1265.115342904267</v>
       </c>
       <c r="J25" t="n">
-        <v>1117.765158147726</v>
+        <v>1265.115342904267</v>
       </c>
       <c r="K25" t="n">
         <v>1265.115342904267</v>
@@ -6165,25 +6165,25 @@
         <v>28.8</v>
       </c>
       <c r="S25" t="n">
-        <v>28.8</v>
+        <v>61.73258797553262</v>
       </c>
       <c r="T25" t="n">
-        <v>221.0966496506082</v>
+        <v>61.73258797553262</v>
       </c>
       <c r="U25" t="n">
-        <v>469.8354499299076</v>
+        <v>311.2697504498848</v>
       </c>
       <c r="V25" t="n">
-        <v>671.6268428158535</v>
+        <v>311.2697504498848</v>
       </c>
       <c r="W25" t="n">
-        <v>671.6268428158535</v>
+        <v>311.2697504498848</v>
       </c>
       <c r="X25" t="n">
-        <v>671.6268428158535</v>
+        <v>465.2705414740784</v>
       </c>
       <c r="Y25" t="n">
-        <v>786.0061434948857</v>
+        <v>579.6498421531106</v>
       </c>
     </row>
     <row r="26">
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>120.8399425761309</v>
+        <v>462.7486213746458</v>
       </c>
       <c r="C26" t="n">
-        <v>120.8399425761309</v>
+        <v>318.8349059776822</v>
       </c>
       <c r="D26" t="n">
-        <v>26.4</v>
+        <v>318.8349059776822</v>
       </c>
       <c r="E26" t="n">
-        <v>26.4</v>
+        <v>220.488148799027</v>
       </c>
       <c r="F26" t="n">
-        <v>26.4</v>
+        <v>121.6097359626514</v>
       </c>
       <c r="G26" t="n">
-        <v>26.4</v>
+        <v>121.6097359626514</v>
       </c>
       <c r="H26" t="n">
         <v>26.4</v>
@@ -6217,25 +6217,25 @@
         <v>26.4</v>
       </c>
       <c r="J26" t="n">
-        <v>353.1</v>
+        <v>47.10481899323997</v>
       </c>
       <c r="K26" t="n">
-        <v>436.1263350753768</v>
+        <v>130.1311540686169</v>
       </c>
       <c r="L26" t="n">
-        <v>539.1278454271356</v>
+        <v>456.8311540686168</v>
       </c>
       <c r="M26" t="n">
-        <v>865.8278454271356</v>
+        <v>783.5311540686187</v>
       </c>
       <c r="N26" t="n">
-        <v>1185.996798811088</v>
+        <v>859.2967988110865</v>
       </c>
       <c r="O26" t="n">
-        <v>1226.424607731732</v>
+        <v>899.72460773173</v>
       </c>
       <c r="P26" t="n">
-        <v>1320</v>
+        <v>993.2999999999981</v>
       </c>
       <c r="Q26" t="n">
         <v>1320</v>
@@ -6244,25 +6244,25 @@
         <v>1320</v>
       </c>
       <c r="S26" t="n">
-        <v>1320</v>
+        <v>1145.429849283477</v>
       </c>
       <c r="T26" t="n">
-        <v>1320</v>
+        <v>865.8444842564008</v>
       </c>
       <c r="U26" t="n">
-        <v>986.6666666666666</v>
+        <v>788.8607669977002</v>
       </c>
       <c r="V26" t="n">
-        <v>660.5545210436121</v>
+        <v>462.7486213746458</v>
       </c>
       <c r="W26" t="n">
-        <v>327.2211877102787</v>
+        <v>462.7486213746458</v>
       </c>
       <c r="X26" t="n">
-        <v>327.2211877102787</v>
+        <v>462.7486213746458</v>
       </c>
       <c r="Y26" t="n">
-        <v>120.8399425761309</v>
+        <v>462.7486213746458</v>
       </c>
     </row>
     <row r="27">
@@ -6287,7 +6287,7 @@
         <v>66.92191566350877</v>
       </c>
       <c r="G27" t="n">
-        <v>48.38102955746751</v>
+        <v>48.34940944326007</v>
       </c>
       <c r="H27" t="n">
         <v>26.4</v>
@@ -6296,19 +6296,19 @@
         <v>26.4</v>
       </c>
       <c r="J27" t="n">
-        <v>26.4</v>
+        <v>183.3508292319027</v>
       </c>
       <c r="K27" t="n">
-        <v>271.9853455283456</v>
+        <v>428.9361747602484</v>
       </c>
       <c r="L27" t="n">
-        <v>419.9759110812524</v>
+        <v>755.6361747602502</v>
       </c>
       <c r="M27" t="n">
-        <v>594.5426528241117</v>
+        <v>930.2029165031095</v>
       </c>
       <c r="N27" t="n">
-        <v>818.6511038467743</v>
+        <v>930.2029165031095</v>
       </c>
       <c r="O27" t="n">
         <v>1140.783583077663</v>
@@ -6390,16 +6390,16 @@
         <v>834.0984889502446</v>
       </c>
       <c r="O28" t="n">
-        <v>539.5082023329253</v>
+        <v>693.0666666667164</v>
       </c>
       <c r="P28" t="n">
-        <v>410.4601798621325</v>
+        <v>359.7333333333584</v>
       </c>
       <c r="Q28" t="n">
-        <v>77.12684652879916</v>
+        <v>26.4</v>
       </c>
       <c r="R28" t="n">
-        <v>77.12684652879916</v>
+        <v>26.4</v>
       </c>
       <c r="S28" t="n">
         <v>26.4</v>
@@ -6430,10 +6430,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>15.68</v>
+        <v>81.67914721196948</v>
       </c>
       <c r="C29" t="n">
-        <v>15.68</v>
+        <v>81.67914721196948</v>
       </c>
       <c r="D29" t="n">
         <v>15.68</v>
@@ -6454,25 +6454,25 @@
         <v>15.68</v>
       </c>
       <c r="J29" t="n">
-        <v>36.38481899323997</v>
+        <v>209.7200000000003</v>
       </c>
       <c r="K29" t="n">
-        <v>119.4111540686169</v>
+        <v>292.7463350753771</v>
       </c>
       <c r="L29" t="n">
-        <v>222.4126644203757</v>
+        <v>395.7478454271359</v>
       </c>
       <c r="M29" t="n">
-        <v>416.4526644203756</v>
+        <v>395.7478454271359</v>
       </c>
       <c r="N29" t="n">
-        <v>610.4926644203756</v>
+        <v>395.7478454271359</v>
       </c>
       <c r="O29" t="n">
-        <v>650.920473341019</v>
+        <v>436.1756543477794</v>
       </c>
       <c r="P29" t="n">
-        <v>744.4958656092872</v>
+        <v>589.9599999999997</v>
       </c>
       <c r="Q29" t="n">
         <v>784</v>
@@ -6484,22 +6484,22 @@
         <v>784</v>
       </c>
       <c r="T29" t="n">
-        <v>784</v>
+        <v>586.0202020202017</v>
       </c>
       <c r="U29" t="n">
-        <v>609.6193939393939</v>
+        <v>388.0404040404035</v>
       </c>
       <c r="V29" t="n">
-        <v>411.639595959596</v>
+        <v>388.0404040404035</v>
       </c>
       <c r="W29" t="n">
-        <v>213.659797979798</v>
+        <v>249.676553962279</v>
       </c>
       <c r="X29" t="n">
-        <v>15.68</v>
+        <v>249.676553962279</v>
       </c>
       <c r="Y29" t="n">
-        <v>15.68</v>
+        <v>81.67914721196948</v>
       </c>
     </row>
     <row r="30">
@@ -6536,16 +6536,16 @@
         <v>172.6308292319027</v>
       </c>
       <c r="K30" t="n">
-        <v>366.6708292319028</v>
+        <v>172.6308292319027</v>
       </c>
       <c r="L30" t="n">
-        <v>366.6708292319028</v>
+        <v>216.7035830776626</v>
       </c>
       <c r="M30" t="n">
-        <v>410.7435830776632</v>
+        <v>216.7035830776626</v>
       </c>
       <c r="N30" t="n">
-        <v>604.7835830776631</v>
+        <v>410.7435830776628</v>
       </c>
       <c r="O30" t="n">
         <v>604.7835830776631</v>
@@ -6588,31 +6588,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>421.0396270384615</v>
+        <v>150.5566496506081</v>
       </c>
       <c r="C31" t="n">
-        <v>492.5916328568973</v>
+        <v>222.1086554690439</v>
       </c>
       <c r="D31" t="n">
-        <v>551.4607769818973</v>
+        <v>222.1086554690439</v>
       </c>
       <c r="E31" t="n">
-        <v>614.8396811933103</v>
+        <v>285.487559680457</v>
       </c>
       <c r="F31" t="n">
-        <v>684.7506537852458</v>
+        <v>355.3985322723925</v>
       </c>
       <c r="G31" t="n">
-        <v>784</v>
+        <v>355.3985322723925</v>
       </c>
       <c r="H31" t="n">
-        <v>784</v>
+        <v>355.3985322723925</v>
       </c>
       <c r="I31" t="n">
-        <v>784</v>
+        <v>500.0298152434592</v>
       </c>
       <c r="J31" t="n">
-        <v>784</v>
+        <v>694.0698152434595</v>
       </c>
       <c r="K31" t="n">
         <v>784</v>
@@ -6627,37 +6627,37 @@
         <v>601.2432920752976</v>
       </c>
       <c r="O31" t="n">
-        <v>411.639595959596</v>
+        <v>601.2432920752976</v>
       </c>
       <c r="P31" t="n">
-        <v>213.659797979798</v>
+        <v>423.9826041045574</v>
       </c>
       <c r="Q31" t="n">
-        <v>15.68</v>
+        <v>226.0028061247591</v>
       </c>
       <c r="R31" t="n">
-        <v>15.68</v>
+        <v>28.02300814496078</v>
       </c>
       <c r="S31" t="n">
         <v>15.68</v>
       </c>
       <c r="T31" t="n">
-        <v>15.68</v>
+        <v>150.5566496506081</v>
       </c>
       <c r="U31" t="n">
-        <v>15.68</v>
+        <v>150.5566496506081</v>
       </c>
       <c r="V31" t="n">
-        <v>92.75127940926619</v>
+        <v>150.5566496506081</v>
       </c>
       <c r="W31" t="n">
-        <v>210.1921976689436</v>
+        <v>150.5566496506081</v>
       </c>
       <c r="X31" t="n">
-        <v>306.7729886931371</v>
+        <v>150.5566496506081</v>
       </c>
       <c r="Y31" t="n">
-        <v>363.7322893721694</v>
+        <v>150.5566496506081</v>
       </c>
     </row>
     <row r="32">
@@ -6694,22 +6694,22 @@
         <v>36.38481899323997</v>
       </c>
       <c r="K32" t="n">
-        <v>230.42481899324</v>
+        <v>119.4111540686169</v>
       </c>
       <c r="L32" t="n">
-        <v>333.4263293449988</v>
+        <v>222.4126644203757</v>
       </c>
       <c r="M32" t="n">
-        <v>455.9567988110885</v>
+        <v>416.4526644203761</v>
       </c>
       <c r="N32" t="n">
-        <v>455.9567988110885</v>
+        <v>416.4526644203761</v>
       </c>
       <c r="O32" t="n">
-        <v>496.3846077317319</v>
+        <v>456.8804733410195</v>
       </c>
       <c r="P32" t="n">
-        <v>589.96</v>
+        <v>650.9204733410199</v>
       </c>
       <c r="Q32" t="n">
         <v>784</v>
@@ -6746,10 +6746,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>15.68</v>
+        <v>213.6597979797984</v>
       </c>
       <c r="C33" t="n">
-        <v>15.68</v>
+        <v>213.6597979797984</v>
       </c>
       <c r="D33" t="n">
         <v>15.68</v>
@@ -6770,52 +6770,52 @@
         <v>15.68</v>
       </c>
       <c r="J33" t="n">
-        <v>27.31325825714086</v>
+        <v>15.68</v>
       </c>
       <c r="K33" t="n">
-        <v>27.31325825714086</v>
+        <v>15.68</v>
       </c>
       <c r="L33" t="n">
-        <v>221.3532582571409</v>
+        <v>209.7200000000004</v>
       </c>
       <c r="M33" t="n">
-        <v>395.9200000000001</v>
+        <v>384.2867417428596</v>
       </c>
       <c r="N33" t="n">
-        <v>589.96</v>
+        <v>578.32674174286</v>
       </c>
       <c r="O33" t="n">
-        <v>784</v>
+        <v>772.3667417428604</v>
       </c>
       <c r="P33" t="n">
         <v>784</v>
       </c>
       <c r="Q33" t="n">
-        <v>654.6561263618178</v>
+        <v>784</v>
       </c>
       <c r="R33" t="n">
-        <v>604.7853572271484</v>
+        <v>734.1292308653307</v>
       </c>
       <c r="S33" t="n">
-        <v>604.7853572271484</v>
+        <v>734.1292308653307</v>
       </c>
       <c r="T33" t="n">
-        <v>604.7853572271484</v>
+        <v>734.1292308653307</v>
       </c>
       <c r="U33" t="n">
-        <v>604.7853572271484</v>
+        <v>536.1494328855323</v>
       </c>
       <c r="V33" t="n">
-        <v>604.7853572271484</v>
+        <v>411.6395959595968</v>
       </c>
       <c r="W33" t="n">
-        <v>411.639595959596</v>
+        <v>213.6597979797984</v>
       </c>
       <c r="X33" t="n">
-        <v>213.659797979798</v>
+        <v>213.6597979797984</v>
       </c>
       <c r="Y33" t="n">
-        <v>15.68</v>
+        <v>213.6597979797984</v>
       </c>
     </row>
     <row r="34">
@@ -6825,76 +6825,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>209.72</v>
+        <v>327.3126177171243</v>
       </c>
       <c r="C34" t="n">
-        <v>209.72</v>
+        <v>521.3526177171248</v>
       </c>
       <c r="D34" t="n">
-        <v>209.72</v>
+        <v>521.3526177171248</v>
       </c>
       <c r="E34" t="n">
-        <v>209.72</v>
+        <v>521.3526177171248</v>
       </c>
       <c r="F34" t="n">
-        <v>209.72</v>
+        <v>521.3526177171248</v>
       </c>
       <c r="G34" t="n">
-        <v>403.76</v>
+        <v>521.3526177171248</v>
       </c>
       <c r="H34" t="n">
-        <v>403.76</v>
+        <v>521.3526177171248</v>
       </c>
       <c r="I34" t="n">
-        <v>473.9142987849217</v>
+        <v>567.661244820196</v>
       </c>
       <c r="J34" t="n">
-        <v>473.9142987849217</v>
+        <v>567.661244820196</v>
       </c>
       <c r="K34" t="n">
-        <v>667.9542987849217</v>
+        <v>761.7012448201964</v>
       </c>
       <c r="L34" t="n">
-        <v>763.4105967447858</v>
+        <v>761.7012448201964</v>
       </c>
       <c r="M34" t="n">
-        <v>763.4105967447858</v>
+        <v>763.4105967447867</v>
       </c>
       <c r="N34" t="n">
-        <v>712.9771211433158</v>
+        <v>712.9771211433166</v>
       </c>
       <c r="O34" t="n">
-        <v>589.0939052330672</v>
+        <v>589.093905233068</v>
       </c>
       <c r="P34" t="n">
-        <v>411.639595959596</v>
+        <v>411.6395959595968</v>
       </c>
       <c r="Q34" t="n">
-        <v>213.659797979798</v>
+        <v>213.6597979797984</v>
       </c>
       <c r="R34" t="n">
         <v>15.68</v>
       </c>
       <c r="S34" t="n">
-        <v>15.68</v>
+        <v>133.2726177171239</v>
       </c>
       <c r="T34" t="n">
-        <v>15.68</v>
+        <v>133.2726177171239</v>
       </c>
       <c r="U34" t="n">
-        <v>209.72</v>
+        <v>327.3126177171243</v>
       </c>
       <c r="V34" t="n">
-        <v>209.72</v>
+        <v>327.3126177171243</v>
       </c>
       <c r="W34" t="n">
-        <v>209.72</v>
+        <v>327.3126177171243</v>
       </c>
       <c r="X34" t="n">
-        <v>209.72</v>
+        <v>327.3126177171243</v>
       </c>
       <c r="Y34" t="n">
-        <v>209.72</v>
+        <v>327.3126177171243</v>
       </c>
     </row>
     <row r="35">
@@ -6928,25 +6928,25 @@
         <v>15.04</v>
       </c>
       <c r="J35" t="n">
-        <v>201.16</v>
+        <v>35.74481899323997</v>
       </c>
       <c r="K35" t="n">
-        <v>284.1863350753769</v>
+        <v>118.7711540686168</v>
       </c>
       <c r="L35" t="n">
-        <v>387.1878454271357</v>
+        <v>221.7726644203756</v>
       </c>
       <c r="M35" t="n">
-        <v>573.3078454271357</v>
+        <v>221.7726644203757</v>
       </c>
       <c r="N35" t="n">
-        <v>617.9967988110884</v>
+        <v>221.7726644203757</v>
       </c>
       <c r="O35" t="n">
-        <v>658.4246077317318</v>
+        <v>407.8926644203757</v>
       </c>
       <c r="P35" t="n">
-        <v>752</v>
+        <v>565.88</v>
       </c>
       <c r="Q35" t="n">
         <v>752</v>
@@ -6983,16 +6983,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>15.04</v>
+        <v>326.3716551077548</v>
       </c>
       <c r="C36" t="n">
-        <v>15.04</v>
+        <v>326.3716551077548</v>
       </c>
       <c r="D36" t="n">
-        <v>15.04</v>
+        <v>326.3716551077548</v>
       </c>
       <c r="E36" t="n">
-        <v>15.04</v>
+        <v>136.4726652087649</v>
       </c>
       <c r="F36" t="n">
         <v>15.04</v>
@@ -7010,49 +7010,49 @@
         <v>171.9908292319027</v>
       </c>
       <c r="K36" t="n">
-        <v>171.9908292319027</v>
+        <v>358.1108292319027</v>
       </c>
       <c r="L36" t="n">
-        <v>205.1932582571408</v>
+        <v>386.6635830776631</v>
       </c>
       <c r="M36" t="n">
-        <v>379.76</v>
+        <v>386.6635830776631</v>
       </c>
       <c r="N36" t="n">
-        <v>565.88</v>
+        <v>386.6635830776631</v>
       </c>
       <c r="O36" t="n">
-        <v>752</v>
+        <v>572.7835830776631</v>
       </c>
       <c r="P36" t="n">
         <v>752</v>
       </c>
       <c r="Q36" t="n">
-        <v>622.6561263618178</v>
+        <v>752</v>
       </c>
       <c r="R36" t="n">
-        <v>576.8257612675525</v>
+        <v>706.1696349057347</v>
       </c>
       <c r="S36" t="n">
-        <v>576.8257612675525</v>
+        <v>706.1696349057347</v>
       </c>
       <c r="T36" t="n">
-        <v>576.8257612675525</v>
+        <v>706.1696349057347</v>
       </c>
       <c r="U36" t="n">
-        <v>576.8257612675525</v>
+        <v>706.1696349057347</v>
       </c>
       <c r="V36" t="n">
-        <v>386.9267713685625</v>
+        <v>706.1696349057347</v>
       </c>
       <c r="W36" t="n">
-        <v>386.9267713685625</v>
+        <v>706.1696349057347</v>
       </c>
       <c r="X36" t="n">
-        <v>197.0277814695726</v>
+        <v>516.2706450067448</v>
       </c>
       <c r="Y36" t="n">
-        <v>197.0277814695726</v>
+        <v>326.3716551077548</v>
       </c>
     </row>
     <row r="37">
@@ -7062,34 +7062,34 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>15.04</v>
+        <v>573.4</v>
       </c>
       <c r="C37" t="n">
-        <v>15.04</v>
+        <v>573.4</v>
       </c>
       <c r="D37" t="n">
-        <v>15.04</v>
+        <v>573.4</v>
       </c>
       <c r="E37" t="n">
-        <v>15.04</v>
+        <v>573.4</v>
       </c>
       <c r="F37" t="n">
-        <v>201.16</v>
+        <v>573.4</v>
       </c>
       <c r="G37" t="n">
-        <v>387.28</v>
+        <v>734.4877684619578</v>
       </c>
       <c r="H37" t="n">
-        <v>448.9514705020936</v>
+        <v>734.4877684619578</v>
       </c>
       <c r="I37" t="n">
-        <v>448.9514705020936</v>
+        <v>734.4877684619578</v>
       </c>
       <c r="J37" t="n">
-        <v>448.9514705020936</v>
+        <v>734.4877684619578</v>
       </c>
       <c r="K37" t="n">
-        <v>635.0714705020936</v>
+        <v>734.4877684619578</v>
       </c>
       <c r="L37" t="n">
         <v>734.4877684619578</v>
@@ -7125,13 +7125,13 @@
         <v>15.04</v>
       </c>
       <c r="W37" t="n">
-        <v>15.04</v>
+        <v>201.16</v>
       </c>
       <c r="X37" t="n">
-        <v>15.04</v>
+        <v>387.28</v>
       </c>
       <c r="Y37" t="n">
-        <v>15.04</v>
+        <v>387.28</v>
       </c>
     </row>
     <row r="38">
@@ -7171,19 +7171,19 @@
         <v>118.7711540686168</v>
       </c>
       <c r="L38" t="n">
-        <v>221.7726644203756</v>
+        <v>304.8911540686169</v>
       </c>
       <c r="M38" t="n">
-        <v>245.7567988110885</v>
+        <v>491.0111540686169</v>
       </c>
       <c r="N38" t="n">
-        <v>431.8767988110885</v>
+        <v>491.0111540686169</v>
       </c>
       <c r="O38" t="n">
-        <v>472.3046077317319</v>
+        <v>565.88</v>
       </c>
       <c r="P38" t="n">
-        <v>565.88</v>
+        <v>752</v>
       </c>
       <c r="Q38" t="n">
         <v>752</v>
@@ -7220,19 +7220,19 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>197.0277814695726</v>
+        <v>516.2706450067448</v>
       </c>
       <c r="C39" t="n">
-        <v>197.0277814695726</v>
+        <v>394.8379797979799</v>
       </c>
       <c r="D39" t="n">
-        <v>197.0277814695726</v>
+        <v>394.8379797979799</v>
       </c>
       <c r="E39" t="n">
-        <v>15.04</v>
+        <v>394.8379797979799</v>
       </c>
       <c r="F39" t="n">
-        <v>15.04</v>
+        <v>204.9389898989899</v>
       </c>
       <c r="G39" t="n">
         <v>15.04</v>
@@ -7244,52 +7244,52 @@
         <v>15.04</v>
       </c>
       <c r="J39" t="n">
-        <v>171.9908292319027</v>
+        <v>15.04</v>
       </c>
       <c r="K39" t="n">
-        <v>171.9908292319027</v>
+        <v>19.07325825714076</v>
       </c>
       <c r="L39" t="n">
-        <v>200.5435830776631</v>
+        <v>205.1932582571408</v>
       </c>
       <c r="M39" t="n">
-        <v>200.5435830776631</v>
+        <v>379.76</v>
       </c>
       <c r="N39" t="n">
-        <v>386.6635830776631</v>
+        <v>565.88</v>
       </c>
       <c r="O39" t="n">
-        <v>572.7835830776631</v>
+        <v>752</v>
       </c>
       <c r="P39" t="n">
         <v>752</v>
       </c>
       <c r="Q39" t="n">
-        <v>622.6561263618178</v>
+        <v>752</v>
       </c>
       <c r="R39" t="n">
-        <v>576.8257612675525</v>
+        <v>706.1696349057347</v>
       </c>
       <c r="S39" t="n">
-        <v>576.8257612675525</v>
+        <v>706.1696349057347</v>
       </c>
       <c r="T39" t="n">
-        <v>576.8257612675525</v>
+        <v>706.1696349057347</v>
       </c>
       <c r="U39" t="n">
-        <v>576.8257612675525</v>
+        <v>706.1696349057347</v>
       </c>
       <c r="V39" t="n">
-        <v>576.8257612675525</v>
+        <v>706.1696349057347</v>
       </c>
       <c r="W39" t="n">
-        <v>386.9267713685625</v>
+        <v>516.2706450067448</v>
       </c>
       <c r="X39" t="n">
-        <v>386.9267713685625</v>
+        <v>516.2706450067448</v>
       </c>
       <c r="Y39" t="n">
-        <v>197.0277814695726</v>
+        <v>516.2706450067448</v>
       </c>
     </row>
     <row r="40">
@@ -7299,46 +7299,46 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>322.712617717124</v>
+        <v>387.28</v>
       </c>
       <c r="C40" t="n">
-        <v>322.712617717124</v>
+        <v>573.4</v>
       </c>
       <c r="D40" t="n">
-        <v>508.832617717124</v>
+        <v>573.4</v>
       </c>
       <c r="E40" t="n">
-        <v>508.832617717124</v>
+        <v>573.4</v>
       </c>
       <c r="F40" t="n">
-        <v>508.832617717124</v>
+        <v>573.4</v>
       </c>
       <c r="G40" t="n">
-        <v>508.832617717124</v>
+        <v>734.4877684619576</v>
       </c>
       <c r="H40" t="n">
-        <v>508.832617717124</v>
+        <v>734.4877684619576</v>
       </c>
       <c r="I40" t="n">
-        <v>508.832617717124</v>
+        <v>734.4877684619576</v>
       </c>
       <c r="J40" t="n">
-        <v>508.832617717124</v>
+        <v>734.4877684619576</v>
       </c>
       <c r="K40" t="n">
-        <v>635.0714705020936</v>
+        <v>734.4877684619576</v>
       </c>
       <c r="L40" t="n">
-        <v>734.4877684619578</v>
+        <v>734.4877684619576</v>
       </c>
       <c r="M40" t="n">
-        <v>734.4877684619578</v>
+        <v>734.4877684619576</v>
       </c>
       <c r="N40" t="n">
-        <v>688.0946969008917</v>
+        <v>688.0946969008914</v>
       </c>
       <c r="O40" t="n">
-        <v>568.2518850310471</v>
+        <v>568.251885031047</v>
       </c>
       <c r="P40" t="n">
         <v>394.8379797979799</v>
@@ -7350,25 +7350,25 @@
         <v>15.04</v>
       </c>
       <c r="S40" t="n">
-        <v>136.5926177171239</v>
+        <v>15.04</v>
       </c>
       <c r="T40" t="n">
-        <v>136.5926177171239</v>
+        <v>15.04</v>
       </c>
       <c r="U40" t="n">
-        <v>136.5926177171239</v>
+        <v>15.04</v>
       </c>
       <c r="V40" t="n">
-        <v>136.5926177171239</v>
+        <v>15.04</v>
       </c>
       <c r="W40" t="n">
-        <v>136.5926177171239</v>
+        <v>201.16</v>
       </c>
       <c r="X40" t="n">
-        <v>136.5926177171239</v>
+        <v>201.16</v>
       </c>
       <c r="Y40" t="n">
-        <v>136.5926177171239</v>
+        <v>201.16</v>
       </c>
     </row>
     <row r="41">
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>153.7664199392422</v>
+        <v>410.5052090079853</v>
       </c>
       <c r="C41" t="n">
-        <v>153.7664199392422</v>
+        <v>410.5052090079853</v>
       </c>
       <c r="D41" t="n">
-        <v>15.04</v>
+        <v>410.5052090079853</v>
       </c>
       <c r="E41" t="n">
-        <v>15.04</v>
+        <v>277.8150174858957</v>
       </c>
       <c r="F41" t="n">
-        <v>15.04</v>
+        <v>144.5931703060857</v>
       </c>
       <c r="G41" t="n">
-        <v>15.04</v>
+        <v>144.5931703060857</v>
       </c>
       <c r="H41" t="n">
         <v>15.04</v>
@@ -7402,25 +7402,25 @@
         <v>15.04</v>
       </c>
       <c r="J41" t="n">
-        <v>35.74481899323997</v>
+        <v>201.16</v>
       </c>
       <c r="K41" t="n">
-        <v>221.86481899324</v>
+        <v>284.1863350753769</v>
       </c>
       <c r="L41" t="n">
-        <v>407.98481899324</v>
+        <v>387.1878454271357</v>
       </c>
       <c r="M41" t="n">
-        <v>431.8767988110885</v>
+        <v>573.3078454271357</v>
       </c>
       <c r="N41" t="n">
-        <v>431.8767988110885</v>
+        <v>573.3078454271357</v>
       </c>
       <c r="O41" t="n">
-        <v>472.3046077317319</v>
+        <v>613.7356543477791</v>
       </c>
       <c r="P41" t="n">
-        <v>565.88</v>
+        <v>752</v>
       </c>
       <c r="Q41" t="n">
         <v>752</v>
@@ -7429,25 +7429,25 @@
         <v>752</v>
       </c>
       <c r="S41" t="n">
-        <v>752</v>
+        <v>562.10101010101</v>
       </c>
       <c r="T41" t="n">
-        <v>752</v>
+        <v>562.10101010101</v>
       </c>
       <c r="U41" t="n">
         <v>562.10101010101</v>
       </c>
       <c r="V41" t="n">
-        <v>533.5643997372221</v>
+        <v>562.10101010101</v>
       </c>
       <c r="W41" t="n">
-        <v>343.6654098382321</v>
+        <v>410.5052090079853</v>
       </c>
       <c r="X41" t="n">
-        <v>153.7664199392422</v>
+        <v>410.5052090079853</v>
       </c>
       <c r="Y41" t="n">
-        <v>153.7664199392422</v>
+        <v>410.5052090079853</v>
       </c>
     </row>
     <row r="42">
@@ -7457,16 +7457,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>426.650039720152</v>
+        <v>213.2702150156145</v>
       </c>
       <c r="C42" t="n">
-        <v>337.6602291691224</v>
+        <v>124.2804044645849</v>
       </c>
       <c r="D42" t="n">
-        <v>261.9655959391198</v>
+        <v>124.2804044645849</v>
       </c>
       <c r="E42" t="n">
-        <v>191.58974015941</v>
+        <v>124.2804044645849</v>
       </c>
       <c r="F42" t="n">
         <v>124.2804044645849</v>
@@ -7484,19 +7484,19 @@
         <v>171.9908292319027</v>
       </c>
       <c r="K42" t="n">
-        <v>171.9908292319027</v>
+        <v>358.1108292319027</v>
       </c>
       <c r="L42" t="n">
-        <v>358.1108292319027</v>
+        <v>386.6635830776631</v>
       </c>
       <c r="M42" t="n">
-        <v>532.6775709747619</v>
+        <v>386.6635830776631</v>
       </c>
       <c r="N42" t="n">
-        <v>718.7975709747619</v>
+        <v>386.6635830776631</v>
       </c>
       <c r="O42" t="n">
-        <v>752</v>
+        <v>572.7835830776631</v>
       </c>
       <c r="P42" t="n">
         <v>752</v>
@@ -7511,22 +7511,22 @@
         <v>752</v>
       </c>
       <c r="T42" t="n">
-        <v>752</v>
+        <v>632.2245578469701</v>
       </c>
       <c r="U42" t="n">
-        <v>752</v>
+        <v>632.2245578469701</v>
       </c>
       <c r="V42" t="n">
-        <v>752</v>
+        <v>489.2844899767478</v>
       </c>
       <c r="W42" t="n">
-        <v>752</v>
+        <v>489.2844899767478</v>
       </c>
       <c r="X42" t="n">
-        <v>667.0015037731429</v>
+        <v>340.9382885167603</v>
       </c>
       <c r="Y42" t="n">
-        <v>539.333430271997</v>
+        <v>213.2702150156145</v>
       </c>
     </row>
     <row r="43">
@@ -7536,55 +7536,55 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>344.0269142947773</v>
+        <v>315.1590827932207</v>
       </c>
       <c r="C43" t="n">
-        <v>344.298920113213</v>
+        <v>315.4310886116565</v>
       </c>
       <c r="D43" t="n">
-        <v>331.6360735924499</v>
+        <v>315.4310886116565</v>
       </c>
       <c r="E43" t="n">
-        <v>323.57455355512</v>
+        <v>315.4310886116565</v>
       </c>
       <c r="F43" t="n">
-        <v>323.57455355512</v>
+        <v>314.0342644018162</v>
       </c>
       <c r="G43" t="n">
-        <v>351.5438997698741</v>
+        <v>342.0036106165703</v>
       </c>
       <c r="H43" t="n">
-        <v>397.9335682079603</v>
+        <v>388.3932790546564</v>
       </c>
       <c r="I43" t="n">
-        <v>502.1411500948628</v>
+        <v>492.600860941559</v>
       </c>
       <c r="J43" t="n">
-        <v>688.2611500948628</v>
+        <v>678.7208609415591</v>
       </c>
       <c r="K43" t="n">
-        <v>706.9113348514034</v>
+        <v>697.3710456980996</v>
       </c>
       <c r="L43" t="n">
-        <v>599.2552772653041</v>
+        <v>697.3710456980996</v>
       </c>
       <c r="M43" t="n">
-        <v>479.9082606702134</v>
+        <v>507.4720557991096</v>
       </c>
       <c r="N43" t="n">
-        <v>479.9082606702134</v>
+        <v>394.8379797979799</v>
       </c>
       <c r="O43" t="n">
-        <v>479.9082606702134</v>
+        <v>394.8379797979799</v>
       </c>
       <c r="P43" t="n">
-        <v>479.9082606702134</v>
+        <v>394.8379797979799</v>
       </c>
       <c r="Q43" t="n">
-        <v>290.0092707712234</v>
+        <v>204.9389898989899</v>
       </c>
       <c r="R43" t="n">
-        <v>100.1102808722335</v>
+        <v>15.04</v>
       </c>
       <c r="S43" t="n">
         <v>15.04</v>
@@ -7605,7 +7605,7 @@
         <v>344.0269142947773</v>
       </c>
       <c r="Y43" t="n">
-        <v>344.0269142947773</v>
+        <v>329.4154467700678</v>
       </c>
     </row>
     <row r="44">
@@ -7648,7 +7648,7 @@
         <v>219.1326644203756</v>
       </c>
       <c r="M44" t="n">
-        <v>372.5826644203756</v>
+        <v>219.1326644203757</v>
       </c>
       <c r="N44" t="n">
         <v>372.5826644203756</v>
@@ -7666,19 +7666,19 @@
         <v>620</v>
       </c>
       <c r="S44" t="n">
+        <v>620</v>
+      </c>
+      <c r="T44" t="n">
         <v>463.4343434343434</v>
       </c>
-      <c r="T44" t="n">
+      <c r="U44" t="n">
         <v>306.8686868686868</v>
       </c>
-      <c r="U44" t="n">
-        <v>150.3030303030303</v>
-      </c>
       <c r="V44" t="n">
-        <v>12.4</v>
+        <v>168.9656565656566</v>
       </c>
       <c r="W44" t="n">
-        <v>12.4</v>
+        <v>168.9656565656566</v>
       </c>
       <c r="X44" t="n">
         <v>12.4</v>
@@ -7694,22 +7694,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>304.1012553109252</v>
+        <v>12.4</v>
       </c>
       <c r="C45" t="n">
-        <v>304.1012553109252</v>
+        <v>12.4</v>
       </c>
       <c r="D45" t="n">
-        <v>304.1012553109252</v>
+        <v>12.4</v>
       </c>
       <c r="E45" t="n">
-        <v>304.1012553109252</v>
+        <v>12.4</v>
       </c>
       <c r="F45" t="n">
-        <v>198.4080812322617</v>
+        <v>12.4</v>
       </c>
       <c r="G45" t="n">
-        <v>107.1083022847403</v>
+        <v>12.4</v>
       </c>
       <c r="H45" t="n">
         <v>12.4</v>
@@ -7721,19 +7721,19 @@
         <v>165.85</v>
       </c>
       <c r="K45" t="n">
-        <v>165.85</v>
+        <v>319.3</v>
       </c>
       <c r="L45" t="n">
         <v>319.3</v>
       </c>
       <c r="M45" t="n">
-        <v>472.7499999999999</v>
+        <v>319.3</v>
       </c>
       <c r="N45" t="n">
-        <v>620</v>
+        <v>466.55</v>
       </c>
       <c r="O45" t="n">
-        <v>620</v>
+        <v>466.55</v>
       </c>
       <c r="P45" t="n">
         <v>620</v>
@@ -7751,19 +7751,19 @@
         <v>463.4343434343434</v>
       </c>
       <c r="U45" t="n">
+        <v>463.4343434343434</v>
+      </c>
+      <c r="V45" t="n">
         <v>306.8686868686868</v>
       </c>
-      <c r="V45" t="n">
-        <v>304.1012553109252</v>
-      </c>
       <c r="W45" t="n">
-        <v>304.1012553109252</v>
+        <v>306.8686868686868</v>
       </c>
       <c r="X45" t="n">
-        <v>304.1012553109252</v>
+        <v>150.3030303030303</v>
       </c>
       <c r="Y45" t="n">
-        <v>304.1012553109252</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>63.4466849046015</v>
+        <v>153.0367844522933</v>
       </c>
       <c r="C46" t="n">
-        <v>63.4466849046015</v>
+        <v>153.0367844522933</v>
       </c>
       <c r="D46" t="n">
+        <v>153.0367844522933</v>
+      </c>
+      <c r="E46" t="n">
+        <v>153.0367844522933</v>
+      </c>
+      <c r="F46" t="n">
+        <v>153.0367844522933</v>
+      </c>
+      <c r="G46" t="n">
+        <v>153.0367844522933</v>
+      </c>
+      <c r="H46" t="n">
+        <v>161.8064528903794</v>
+      </c>
+      <c r="I46" t="n">
+        <v>228.3940347772819</v>
+      </c>
+      <c r="J46" t="n">
+        <v>381.8440347772819</v>
+      </c>
+      <c r="K46" t="n">
+        <v>381.8440347772819</v>
+      </c>
+      <c r="L46" t="n">
+        <v>235.8041388073444</v>
+      </c>
+      <c r="M46" t="n">
+        <v>235.8041388073444</v>
+      </c>
+      <c r="N46" t="n">
+        <v>79.23848224168779</v>
+      </c>
+      <c r="O46" t="n">
+        <v>79.23848224168779</v>
+      </c>
+      <c r="P46" t="n">
+        <v>79.23848224168779</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>79.23848224168779</v>
+      </c>
+      <c r="R46" t="n">
+        <v>79.23848224168779</v>
+      </c>
+      <c r="S46" t="n">
         <v>12.4</v>
       </c>
-      <c r="E46" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="F46" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="G46" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="H46" t="n">
-        <v>21.1696684380861</v>
-      </c>
-      <c r="I46" t="n">
-        <v>87.75725032498866</v>
-      </c>
-      <c r="J46" t="n">
-        <v>241.2072503249886</v>
-      </c>
-      <c r="K46" t="n">
-        <v>221.852270992819</v>
-      </c>
-      <c r="L46" t="n">
-        <v>221.852270992819</v>
-      </c>
-      <c r="M46" t="n">
-        <v>221.852270992819</v>
-      </c>
-      <c r="N46" t="n">
-        <v>221.852270992819</v>
-      </c>
-      <c r="O46" t="n">
-        <v>221.852270992819</v>
-      </c>
-      <c r="P46" t="n">
-        <v>221.852270992819</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>221.852270992819</v>
-      </c>
-      <c r="R46" t="n">
-        <v>139.330189159323</v>
-      </c>
-      <c r="S46" t="n">
-        <v>15.87606990325112</v>
-      </c>
       <c r="T46" t="n">
-        <v>41.85271955385926</v>
+        <v>38.37664965060814</v>
       </c>
       <c r="U46" t="n">
-        <v>125.0698820282115</v>
+        <v>121.5938121249604</v>
       </c>
       <c r="V46" t="n">
-        <v>160.5412749141574</v>
+        <v>157.0652050109063</v>
       </c>
       <c r="W46" t="n">
-        <v>169.0821931738348</v>
+        <v>165.6061232705837</v>
       </c>
       <c r="X46" t="n">
-        <v>169.0821931738348</v>
+        <v>153.0367844522933</v>
       </c>
       <c r="Y46" t="n">
-        <v>116.086887265287</v>
+        <v>153.0367844522933</v>
       </c>
     </row>
   </sheetData>
@@ -7964,28 +7964,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>163.0860414209697</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>79.95807035175875</v>
       </c>
       <c r="M2" t="n">
-        <v>428.4954341749806</v>
+        <v>612.4954341749806</v>
       </c>
       <c r="N2" t="n">
-        <v>396.9110115869491</v>
+        <v>359.6090384718453</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>30.95054243509064</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>89.47940174922412</v>
       </c>
       <c r="Q2" t="n">
-        <v>285.62608131241</v>
+        <v>101.62608131241</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8043,25 +8043,25 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J3" t="n">
-        <v>227.4647419277884</v>
+        <v>68.92855078445234</v>
       </c>
       <c r="K3" t="n">
-        <v>231.8142352788259</v>
+        <v>47.81423527882597</v>
       </c>
       <c r="L3" t="n">
         <v>221.4053196016771</v>
       </c>
       <c r="M3" t="n">
-        <v>316.3675599279874</v>
+        <v>471.6948204301074</v>
       </c>
       <c r="N3" t="n">
-        <v>259.036354421186</v>
+        <v>443.036354421186</v>
       </c>
       <c r="O3" t="n">
-        <v>57.29545614344035</v>
+        <v>241.2954561434403</v>
       </c>
       <c r="P3" t="n">
-        <v>219.1507118405495</v>
+        <v>38.3596424817656</v>
       </c>
       <c r="Q3" t="n">
         <v>17.27519534353338</v>
@@ -8204,16 +8204,16 @@
         <v>297.0860414209697</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>85.92976134920366</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>213.9580703517588</v>
       </c>
       <c r="M5" t="n">
         <v>746.4954341749806</v>
       </c>
       <c r="N5" t="n">
-        <v>659.4968701728078</v>
+        <v>359.6090384718453</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -8292,13 +8292,13 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N6" t="n">
-        <v>485.4085271713503</v>
+        <v>436.2289469207369</v>
       </c>
       <c r="O6" t="n">
         <v>57.29545614344035</v>
       </c>
       <c r="P6" t="n">
-        <v>169.9711315899361</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q6" t="n">
         <v>17.27519534353338</v>
@@ -8438,28 +8438,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>278.9738731219322</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.810043748844748</v>
       </c>
       <c r="M8" t="n">
-        <v>746.4954341749806</v>
+        <v>428.4954341749806</v>
       </c>
       <c r="N8" t="n">
         <v>677.6090384718452</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>277.1638293730874</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>101.62608131241</v>
+        <v>419.62608131241</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8520,16 +8520,16 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K9" t="n">
-        <v>47.81423527882597</v>
+        <v>295.8802408630135</v>
       </c>
       <c r="L9" t="n">
-        <v>236.2917449352514</v>
+        <v>214.5979121012281</v>
       </c>
       <c r="M9" t="n">
         <v>471.6948204301074</v>
       </c>
       <c r="N9" t="n">
-        <v>485.4085271713503</v>
+        <v>259.036354421186</v>
       </c>
       <c r="O9" t="n">
         <v>375.2954561434403</v>
@@ -8675,25 +8675,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>305.0860414209697</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>242.1350150753769</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>73.42958430235316</v>
+        <v>104.0074096763882</v>
       </c>
       <c r="M11" t="n">
-        <v>754.4954341749806</v>
+        <v>428.4954341749806</v>
       </c>
       <c r="N11" t="n">
-        <v>359.6090384718453</v>
+        <v>685.6090384718452</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>285.1638293730874</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>231.4794017492241</v>
       </c>
       <c r="Q11" t="n">
         <v>101.62608131241</v>
@@ -8757,13 +8757,13 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K12" t="n">
-        <v>295.8802408630135</v>
+        <v>121.3211277962087</v>
       </c>
       <c r="L12" t="n">
-        <v>193.5428481303044</v>
+        <v>363.4053196016771</v>
       </c>
       <c r="M12" t="n">
-        <v>471.6948204301074</v>
+        <v>295.3647782656031</v>
       </c>
       <c r="N12" t="n">
         <v>485.4085271713503</v>
@@ -8772,7 +8772,7 @@
         <v>382.6817988009037</v>
       </c>
       <c r="P12" t="n">
-        <v>38.12402808061323</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q12" t="n">
         <v>17.27519534353338</v>
@@ -8915,25 +8915,25 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>242.1350150753769</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>221.9580703517588</v>
       </c>
       <c r="M14" t="n">
-        <v>723.1460749736805</v>
+        <v>754.4954341749806</v>
       </c>
       <c r="N14" t="n">
-        <v>685.6090384718452</v>
+        <v>359.6090384718453</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>156.5575553715641</v>
       </c>
       <c r="Q14" t="n">
-        <v>427.62608131241</v>
+        <v>101.62608131241</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -8994,7 +8994,7 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K15" t="n">
-        <v>295.8802408630135</v>
+        <v>171.3632583818687</v>
       </c>
       <c r="L15" t="n">
         <v>363.4053196016771</v>
@@ -9003,13 +9003,13 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N15" t="n">
-        <v>315.5460556999775</v>
+        <v>259.036354421186</v>
       </c>
       <c r="O15" t="n">
         <v>382.6817988009037</v>
       </c>
       <c r="P15" t="n">
-        <v>38.12402808061323</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q15" t="n">
         <v>17.27519534353338</v>
@@ -9149,19 +9149,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>305.0860414209697</v>
+        <v>156.5575553715642</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>242.1350150753769</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>221.9580703517588</v>
       </c>
       <c r="M17" t="n">
-        <v>744.0600335527107</v>
+        <v>428.4954341749806</v>
       </c>
       <c r="N17" t="n">
-        <v>685.6090384718452</v>
+        <v>359.6090384718453</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9170,7 +9170,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>101.62608131241</v>
+        <v>427.62608131241</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9228,13 +9228,13 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J18" t="n">
-        <v>227.4647419277884</v>
+        <v>68.92855078445234</v>
       </c>
       <c r="K18" t="n">
-        <v>295.8802408630135</v>
+        <v>103.5272767750405</v>
       </c>
       <c r="L18" t="n">
-        <v>37.40531960167714</v>
+        <v>363.4053196016771</v>
       </c>
       <c r="M18" t="n">
         <v>471.6948204301074</v>
@@ -9243,7 +9243,7 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O18" t="n">
-        <v>357.7926435695946</v>
+        <v>382.6817988009037</v>
       </c>
       <c r="P18" t="n">
         <v>219.1507118405495</v>
@@ -9386,28 +9386,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3173074653592423</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>275.1350150753769</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>254.9580703517588</v>
       </c>
       <c r="M20" t="n">
-        <v>787.495434174983</v>
+        <v>428.4954341749806</v>
       </c>
       <c r="N20" t="n">
-        <v>718.6090384718477</v>
+        <v>718.6090384718473</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>188.2242220382289</v>
       </c>
       <c r="Q20" t="n">
-        <v>460.6260813124125</v>
+        <v>101.62608131241</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9465,10 +9465,10 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J21" t="n">
-        <v>227.4647419277884</v>
+        <v>68.92855078445234</v>
       </c>
       <c r="K21" t="n">
-        <v>50.97373544025017</v>
+        <v>295.8802408630135</v>
       </c>
       <c r="L21" t="n">
         <v>388.0893364597981</v>
@@ -9483,7 +9483,7 @@
         <v>382.6817988009037</v>
       </c>
       <c r="P21" t="n">
-        <v>219.1507118405495</v>
+        <v>132.7803975611224</v>
       </c>
       <c r="Q21" t="n">
         <v>17.27519534353338</v>
@@ -9623,28 +9623,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>339.0860414209762</v>
       </c>
       <c r="K23" t="n">
-        <v>276.1350150753768</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>788.4954341749806</v>
+        <v>428.4954341749806</v>
       </c>
       <c r="N23" t="n">
-        <v>444.7509268214307</v>
+        <v>359.6090384718453</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>116.711460254749</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>265.4794017492306</v>
       </c>
       <c r="Q23" t="n">
-        <v>461.62608131241</v>
+        <v>461.6260813124166</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9702,22 +9702,22 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J24" t="n">
-        <v>68.92855078445234</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K24" t="n">
-        <v>213.4695225431822</v>
+        <v>295.8802408630135</v>
       </c>
       <c r="L24" t="n">
         <v>388.0893364597981</v>
       </c>
       <c r="M24" t="n">
-        <v>471.6948204301074</v>
+        <v>295.3647782656031</v>
       </c>
       <c r="N24" t="n">
         <v>485.4085271713503</v>
       </c>
       <c r="O24" t="n">
-        <v>382.6817988009037</v>
+        <v>318.0649315022406</v>
       </c>
       <c r="P24" t="n">
         <v>219.1507118405495</v>
@@ -9860,19 +9860,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>309.0860414209697</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>225.9580703517587</v>
       </c>
       <c r="M26" t="n">
-        <v>758.4954341749806</v>
+        <v>758.4954341749825</v>
       </c>
       <c r="N26" t="n">
-        <v>683.0120216879593</v>
+        <v>436.1399927571664</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -9881,7 +9881,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>101.62608131241</v>
+        <v>431.6260813124119</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -9939,22 +9939,22 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J27" t="n">
-        <v>68.92855078445234</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K27" t="n">
         <v>295.8802408630135</v>
       </c>
       <c r="L27" t="n">
-        <v>186.890739352088</v>
+        <v>367.405319601679</v>
       </c>
       <c r="M27" t="n">
         <v>471.6948204301074</v>
       </c>
       <c r="N27" t="n">
-        <v>485.4085271713503</v>
+        <v>259.036354421186</v>
       </c>
       <c r="O27" t="n">
-        <v>382.6817988009037</v>
+        <v>270.0032001581409</v>
       </c>
       <c r="P27" t="n">
         <v>219.1507118405495</v>
@@ -10097,7 +10097,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>175.08604142097</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -10106,19 +10106,19 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>624.4954341749806</v>
+        <v>428.4954341749806</v>
       </c>
       <c r="N29" t="n">
-        <v>555.6090384718452</v>
+        <v>359.6090384718453</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>60.81712463025478</v>
       </c>
       <c r="Q29" t="n">
-        <v>141.5292473636351</v>
+        <v>297.6260813124103</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10179,19 +10179,19 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K30" t="n">
-        <v>243.8142352788259</v>
+        <v>47.81423527882597</v>
       </c>
       <c r="L30" t="n">
-        <v>37.40531960167714</v>
+        <v>81.92325277921231</v>
       </c>
       <c r="M30" t="n">
-        <v>339.8827114431389</v>
+        <v>295.3647782656031</v>
       </c>
       <c r="N30" t="n">
-        <v>455.036354421186</v>
+        <v>455.0363544211862</v>
       </c>
       <c r="O30" t="n">
-        <v>57.29545614344035</v>
+        <v>253.2954561434407</v>
       </c>
       <c r="P30" t="n">
         <v>219.1507118405495</v>
@@ -10337,13 +10337,13 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>112.1350150753769</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>552.2635851508288</v>
+        <v>624.4954341749809</v>
       </c>
       <c r="N32" t="n">
         <v>359.6090384718453</v>
@@ -10352,10 +10352,10 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>101.4794017492245</v>
       </c>
       <c r="Q32" t="n">
-        <v>297.62608131241</v>
+        <v>236.0498456144101</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10413,25 +10413,25 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J33" t="n">
-        <v>80.67931670075625</v>
+        <v>68.92855078445234</v>
       </c>
       <c r="K33" t="n">
         <v>47.81423527882597</v>
       </c>
       <c r="L33" t="n">
-        <v>233.4053196016771</v>
+        <v>233.4053196016775</v>
       </c>
       <c r="M33" t="n">
         <v>471.6948204301074</v>
       </c>
       <c r="N33" t="n">
-        <v>455.036354421186</v>
+        <v>455.0363544211864</v>
       </c>
       <c r="O33" t="n">
-        <v>253.2954561434403</v>
+        <v>253.2954561434408</v>
       </c>
       <c r="P33" t="n">
-        <v>38.12402808061323</v>
+        <v>49.87479399691583</v>
       </c>
       <c r="Q33" t="n">
         <v>17.27519534353338</v>
@@ -10571,7 +10571,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>167.0860414209697</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -10580,19 +10580,19 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>616.4954341749806</v>
+        <v>428.4954341749806</v>
       </c>
       <c r="N35" t="n">
-        <v>404.7493954253329</v>
+        <v>359.6090384718453</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>147.1638293730874</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>65.06256900136988</v>
       </c>
       <c r="Q35" t="n">
-        <v>101.62608131241</v>
+        <v>289.62608131241</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10653,22 +10653,22 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K36" t="n">
-        <v>47.81423527882597</v>
+        <v>235.8142352788259</v>
       </c>
       <c r="L36" t="n">
-        <v>70.94312669787718</v>
+        <v>66.24648510244525</v>
       </c>
       <c r="M36" t="n">
-        <v>471.6948204301074</v>
+        <v>295.3647782656031</v>
       </c>
       <c r="N36" t="n">
-        <v>447.036354421186</v>
+        <v>259.036354421186</v>
       </c>
       <c r="O36" t="n">
         <v>245.2954561434403</v>
       </c>
       <c r="P36" t="n">
-        <v>38.12402808061323</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q36" t="n">
         <v>17.27519534353338</v>
@@ -10814,22 +10814,22 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>83.95807035175878</v>
       </c>
       <c r="M38" t="n">
-        <v>452.721832549438</v>
+        <v>616.4954341749806</v>
       </c>
       <c r="N38" t="n">
-        <v>547.6090384718452</v>
+        <v>359.6090384718453</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>34.78892627347443</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>93.47940174922412</v>
       </c>
       <c r="Q38" t="n">
-        <v>289.62608131241</v>
+        <v>101.62608131241</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -10887,16 +10887,16 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J39" t="n">
-        <v>227.4647419277884</v>
+        <v>68.92855078445234</v>
       </c>
       <c r="K39" t="n">
-        <v>47.81423527882597</v>
+        <v>51.88823351836209</v>
       </c>
       <c r="L39" t="n">
-        <v>66.24648510244522</v>
+        <v>225.4053196016771</v>
       </c>
       <c r="M39" t="n">
-        <v>295.3647782656031</v>
+        <v>471.6948204301074</v>
       </c>
       <c r="N39" t="n">
         <v>447.036354421186</v>
@@ -10905,7 +10905,7 @@
         <v>245.2954561434403</v>
       </c>
       <c r="P39" t="n">
-        <v>219.1507118405495</v>
+        <v>38.12402808061323</v>
       </c>
       <c r="Q39" t="n">
         <v>17.27519534353338</v>
@@ -11045,16 +11045,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>167.0860414209697</v>
       </c>
       <c r="K41" t="n">
-        <v>104.1350150753769</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>83.95807035175875</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>452.6287471223023</v>
+        <v>616.4954341749806</v>
       </c>
       <c r="N41" t="n">
         <v>359.6090384718453</v>
@@ -11063,10 +11063,10 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>45.14035695348763</v>
       </c>
       <c r="Q41" t="n">
-        <v>289.62608131241</v>
+        <v>101.62608131241</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11127,22 +11127,22 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K42" t="n">
-        <v>47.81423527882597</v>
+        <v>235.8142352788259</v>
       </c>
       <c r="L42" t="n">
-        <v>225.4053196016771</v>
+        <v>66.24648510244525</v>
       </c>
       <c r="M42" t="n">
-        <v>471.6948204301074</v>
+        <v>295.3647782656031</v>
       </c>
       <c r="N42" t="n">
-        <v>447.036354421186</v>
+        <v>259.036354421186</v>
       </c>
       <c r="O42" t="n">
-        <v>90.83326323964042</v>
+        <v>245.2954561434403</v>
       </c>
       <c r="P42" t="n">
-        <v>38.12402808061323</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q42" t="n">
         <v>17.27519534353338</v>
@@ -11291,10 +11291,10 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>583.4954341749806</v>
+        <v>428.4954341749806</v>
       </c>
       <c r="N44" t="n">
-        <v>359.6090384718453</v>
+        <v>514.6090384718452</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -11364,13 +11364,13 @@
         <v>223.9285507844523</v>
       </c>
       <c r="K45" t="n">
-        <v>47.81423527882597</v>
+        <v>202.8142352788259</v>
       </c>
       <c r="L45" t="n">
-        <v>192.4053196016771</v>
+        <v>37.40531960167714</v>
       </c>
       <c r="M45" t="n">
-        <v>450.3647782656031</v>
+        <v>295.3647782656031</v>
       </c>
       <c r="N45" t="n">
         <v>407.7737281585598</v>
@@ -11379,7 +11379,7 @@
         <v>57.29545614344035</v>
       </c>
       <c r="P45" t="n">
-        <v>38.12402808061323</v>
+        <v>193.1240280806132</v>
       </c>
       <c r="Q45" t="n">
         <v>17.27519534353338</v>
@@ -22521,7 +22521,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.3632896068686478</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -22563,25 +22563,25 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>75.82444920935808</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>179.7895113768051</v>
+        <v>40.24943623259333</v>
       </c>
       <c r="U2" t="n">
-        <v>245.1685528300177</v>
+        <v>61.16855283001769</v>
       </c>
       <c r="V2" t="n">
-        <v>118.1672221029291</v>
+        <v>41.85102416682389</v>
       </c>
       <c r="W2" t="n">
-        <v>50.37347598094755</v>
+        <v>234.3734759809475</v>
       </c>
       <c r="X2" t="n">
-        <v>4.281833460667713</v>
+        <v>188.2818334606677</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>107.3174326828064</v>
       </c>
     </row>
     <row r="3">
@@ -22706,7 +22706,7 @@
         <v>70.27338189435318</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>121.9291408454554</v>
       </c>
       <c r="O4" t="n">
         <v>10.64438375114611</v>
@@ -22718,7 +22718,7 @@
         <v>113.075266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>269.1666262036558</v>
+        <v>147.2374853582004</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -22800,10 +22800,10 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>74.82444920935808</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>67.50047743648665</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -22812,7 +22812,7 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>142.3249266458446</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -22940,7 +22940,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.8122244554895488</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -22955,7 +22955,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8122244554894564</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -22989,7 +22989,7 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>44.47457824299391</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -23037,19 +23037,19 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>74.82444920935808</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>23.0258991934929</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>142.3249266458446</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -23223,13 +23223,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>173.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>102.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>96.36328960686865</v>
@@ -23238,7 +23238,7 @@
         <v>96.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>95.09807580460415</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>93.2576386030249</v>
@@ -23280,19 +23280,19 @@
         <v>275.7895113768051</v>
       </c>
       <c r="U11" t="n">
-        <v>341.1685528300177</v>
+        <v>15.16855283000575</v>
       </c>
       <c r="V11" t="n">
-        <v>11.78406855329945</v>
+        <v>179.903180370526</v>
       </c>
       <c r="W11" t="n">
-        <v>4.373475980940157</v>
+        <v>330.3734759809475</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>203.3174326828064</v>
       </c>
     </row>
     <row r="12">
@@ -23317,10 +23317,10 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5545039130498808</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>0.5545039130651865</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -23411,28 +23411,28 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>71.57949701023819</v>
       </c>
       <c r="M13" t="n">
         <v>166.2733818943532</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>217.9291408454554</v>
       </c>
       <c r="O13" t="n">
-        <v>16.23179967035094</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>343.6797661807365</v>
+        <v>17.67976618071509</v>
       </c>
       <c r="Q13" t="n">
         <v>67.075266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>79.30468535820025</v>
+        <v>82.80826910936776</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>49.21957806351117</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -23460,13 +23460,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>173.9993129555745</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>141.4745782429939</v>
       </c>
       <c r="D14" t="n">
-        <v>102.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>96.36328960686865</v>
@@ -23475,10 +23475,10 @@
         <v>96.88962870801186</v>
       </c>
       <c r="G14" t="n">
-        <v>95.09807580460415</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>93.25763860302487</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23517,19 +23517,19 @@
         <v>275.7895113768051</v>
       </c>
       <c r="U14" t="n">
-        <v>15.16855283001587</v>
+        <v>15.16855283001588</v>
       </c>
       <c r="V14" t="n">
-        <v>321.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>4.373475980945784</v>
+        <v>207.0960029780586</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>284.2818334606677</v>
       </c>
       <c r="Y14" t="n">
-        <v>189.9323573420462</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -23557,7 +23557,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>0.5545039130651865</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -23587,7 +23587,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5545039130652469</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -23660,16 +23660,16 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>17.67976618073652</v>
+        <v>17.6797661807365</v>
       </c>
       <c r="Q16" t="n">
-        <v>70.57885017674414</v>
+        <v>119.7984282402553</v>
       </c>
       <c r="R16" t="n">
-        <v>79.30468535820023</v>
+        <v>79.30468535820025</v>
       </c>
       <c r="S16" t="n">
-        <v>49.21957806351116</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23748,10 +23748,10 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>75.82444920935808</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>46.70699575136701</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -23763,7 +23763,7 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>122.5314449607253</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
@@ -23934,7 +23934,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>6.563120765328563</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -24003,7 +24003,7 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.563120765328549</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -24222,13 +24222,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.584244960725115</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.584244960725158</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -24411,22 +24411,22 @@
         <v>174.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>142.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>9.843612589480244</v>
+        <v>103.3391557398498</v>
       </c>
       <c r="E26" t="n">
-        <v>97.36328960686865</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>97.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>96.09807580460415</v>
       </c>
       <c r="H26" t="n">
-        <v>94.2576386030249</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24459,25 +24459,25 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>172.8244492093581</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>276.7895113768051</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>12.1685528300177</v>
+        <v>265.9546727439041</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.373475980947546</v>
+        <v>331.3734759809475</v>
       </c>
       <c r="X26" t="n">
         <v>285.2818334606677</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>204.3174326828064</v>
       </c>
     </row>
     <row r="27">
@@ -24502,10 +24502,10 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.03130391306536068</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>0.0313039130653614</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -24605,19 +24605,19 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>152.0228796904532</v>
       </c>
       <c r="P28" t="n">
-        <v>216.9222239346517</v>
+        <v>14.67976618071202</v>
       </c>
       <c r="Q28" t="n">
-        <v>64.075266425598</v>
+        <v>64.0752664255732</v>
       </c>
       <c r="R28" t="n">
         <v>406.3046853582002</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>50.21957806351117</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24651,7 +24651,7 @@
         <v>104.4745782429939</v>
       </c>
       <c r="D29" t="n">
-        <v>65.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>59.36328960686865</v>
@@ -24699,22 +24699,22 @@
         <v>134.8244492093581</v>
       </c>
       <c r="T29" t="n">
-        <v>238.7895113768051</v>
+        <v>42.7895113768048</v>
       </c>
       <c r="U29" t="n">
-        <v>131.5317528300177</v>
+        <v>108.1685528300174</v>
       </c>
       <c r="V29" t="n">
-        <v>88.85102416682389</v>
+        <v>284.8510241668239</v>
       </c>
       <c r="W29" t="n">
-        <v>97.37347598094755</v>
+        <v>156.3932644036043</v>
       </c>
       <c r="X29" t="n">
-        <v>51.28183346066771</v>
+        <v>247.2818334606677</v>
       </c>
       <c r="Y29" t="n">
-        <v>166.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -24842,19 +24842,19 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>65.93672459660147</v>
+        <v>253.6443837511461</v>
       </c>
       <c r="P31" t="n">
-        <v>110.6797661807365</v>
+        <v>131.1916850897037</v>
       </c>
       <c r="Q31" t="n">
-        <v>160.075266425598</v>
+        <v>160.0752664255976</v>
       </c>
       <c r="R31" t="n">
-        <v>368.3046853582002</v>
+        <v>172.3046853581999</v>
       </c>
       <c r="S31" t="n">
-        <v>12.21957806351118</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -25085,10 +25085,10 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>29.075266425598</v>
+        <v>29.07526642559754</v>
       </c>
       <c r="R34" t="n">
-        <v>41.30468535820025</v>
+        <v>41.30468535819979</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -25559,10 +25559,10 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>33.075266425598</v>
+        <v>33.07526642559799</v>
       </c>
       <c r="R40" t="n">
-        <v>45.30468535820025</v>
+        <v>45.30468535820023</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -25599,19 +25599,19 @@
         <v>176.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>137.3391557398498</v>
       </c>
       <c r="E41" t="n">
-        <v>131.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>131.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>130.0980758046042</v>
       </c>
       <c r="H41" t="n">
-        <v>128.2576386030249</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25644,22 +25644,22 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>206.8244492093581</v>
+        <v>18.82444920935808</v>
       </c>
       <c r="T41" t="n">
         <v>310.7895113768051</v>
       </c>
       <c r="U41" t="n">
-        <v>188.1685528300177</v>
+        <v>376.1685528300177</v>
       </c>
       <c r="V41" t="n">
-        <v>328.5997799066738</v>
+        <v>356.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>177.3734759809475</v>
+        <v>215.293632898853</v>
       </c>
       <c r="X41" t="n">
-        <v>131.2818334606677</v>
+        <v>319.2818334606677</v>
       </c>
       <c r="Y41" t="n">
         <v>238.3174326828064</v>
@@ -25672,19 +25672,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>111.5565566463266</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>74.93768689770263</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>69.67209722191262</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>66.63624233787687</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -25726,19 +25726,19 @@
         <v>187.0117358136679</v>
       </c>
       <c r="T42" t="n">
-        <v>130.93591616091</v>
+        <v>12.35822842941047</v>
       </c>
       <c r="U42" t="n">
         <v>127.1871522130169</v>
       </c>
       <c r="V42" t="n">
-        <v>141.5106671915202</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
         <v>159.3731429098285</v>
       </c>
       <c r="X42" t="n">
-        <v>62.714228180799</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
@@ -25751,19 +25751,19 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>14.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>12.53621805555548</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>7.98090483695654</v>
       </c>
       <c r="F43" t="n">
-        <v>1.382855967741932</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -25781,13 +25781,13 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>106.5794970102382</v>
       </c>
       <c r="M43" t="n">
-        <v>83.11983546521336</v>
+        <v>13.27338189435318</v>
       </c>
       <c r="N43" t="n">
-        <v>252.9291408454554</v>
+        <v>141.421405604337</v>
       </c>
       <c r="O43" t="n">
         <v>325.6443837511461</v>
@@ -25802,7 +25802,7 @@
         <v>252.3046853582002</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>84.21957806351116</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -25820,7 +25820,7 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>14.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -25881,7 +25881,7 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>89.82444920935808</v>
+        <v>244.8244492093581</v>
       </c>
       <c r="T44" t="n">
         <v>193.7895113768051</v>
@@ -25896,7 +25896,7 @@
         <v>403.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>357.2818334606677</v>
+        <v>202.2818334606677</v>
       </c>
       <c r="Y44" t="n">
         <v>276.3174326828064</v>
@@ -25921,13 +25921,13 @@
         <v>107.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>104.6362423378769</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>90.38678115804623</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>93.76121926189285</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -25966,19 +25966,19 @@
         <v>13.93591616091004</v>
       </c>
       <c r="U45" t="n">
-        <v>10.18715221301693</v>
+        <v>165.1871522130169</v>
       </c>
       <c r="V45" t="n">
-        <v>176.7709099493362</v>
+        <v>24.51066719152016</v>
       </c>
       <c r="W45" t="n">
         <v>197.3731429098285</v>
       </c>
       <c r="X45" t="n">
-        <v>184.8627394453875</v>
+        <v>29.86273944538755</v>
       </c>
       <c r="Y45" t="n">
-        <v>164.3913927661343</v>
+        <v>27.8673927661344</v>
       </c>
     </row>
     <row r="46">
@@ -25988,13 +25988,13 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>52.11380033707866</v>
       </c>
       <c r="C46" t="n">
         <v>37.72524664804467</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>50.53621805555548</v>
       </c>
       <c r="E46" t="n">
         <v>45.98090483695654</v>
@@ -26015,16 +26015,16 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>19.16142953884798</v>
       </c>
       <c r="L46" t="n">
-        <v>144.5794970102382</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>239.2733818943532</v>
       </c>
       <c r="N46" t="n">
-        <v>290.9291408454554</v>
+        <v>135.9291408454554</v>
       </c>
       <c r="O46" t="n">
         <v>363.6443837511461</v>
@@ -26036,10 +26036,10 @@
         <v>466.075266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>396.6078243430392</v>
+        <v>478.3046853582002</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>56.04948064424026</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -26054,10 +26054,10 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>12.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>52.46535284946236</v>
       </c>
     </row>
   </sheetData>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>957117.8795735063</v>
+        <v>957117.8795735064</v>
       </c>
     </row>
     <row r="3">
@@ -26094,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1891067.693228743</v>
+        <v>1891067.693228744</v>
       </c>
     </row>
     <row r="4">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3614532.859364961</v>
+        <v>3614532.85936496</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>4431438.320936848</v>
+        <v>4431438.320936847</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5337415.385489293</v>
+        <v>5337415.385489292</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6257258.582031054</v>
+        <v>6257258.582031053</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7170369.521358998</v>
+        <v>7170369.521358995</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7980601.086819733</v>
+        <v>7980601.086819731</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8765545.314765539</v>
+        <v>8765545.314765537</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9677369.057845628</v>
+        <v>9677369.057845626</v>
       </c>
     </row>
     <row r="13">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12208630.10488714</v>
+        <v>12208630.10488713</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12835870.35090747</v>
+        <v>12835870.35090746</v>
       </c>
     </row>
   </sheetData>
@@ -26278,10 +26278,10 @@
         <v>1279229.194854271</v>
       </c>
       <c r="E2" t="n">
-        <v>1154935.307739566</v>
+        <v>1154935.307739565</v>
       </c>
       <c r="F2" t="n">
-        <v>1154935.307739566</v>
+        <v>1154935.307739565</v>
       </c>
       <c r="G2" t="n">
         <v>1280864.125746564</v>
@@ -26290,7 +26290,7 @@
         <v>1290325.981317668</v>
       </c>
       <c r="I2" t="n">
-        <v>1290642.615789667</v>
+        <v>1290642.615789668</v>
       </c>
       <c r="J2" t="n">
         <v>1154719.78690531</v>
@@ -26311,7 +26311,7 @@
         <v>1003271.43560334</v>
       </c>
       <c r="P2" t="n">
-        <v>896929.9202356214</v>
+        <v>896929.9202356212</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>604599.5226031976</v>
+        <v>604590.0918763465</v>
       </c>
       <c r="C4" t="n">
-        <v>627780.6117219813</v>
+        <v>627768.1986006544</v>
       </c>
       <c r="D4" t="n">
-        <v>625751.017053582</v>
+        <v>625738.6039322552</v>
       </c>
       <c r="E4" t="n">
-        <v>554733.2637991172</v>
+        <v>554720.6726243882</v>
       </c>
       <c r="F4" t="n">
-        <v>552986.5997075147</v>
+        <v>552974.0085327863</v>
       </c>
       <c r="G4" t="n">
-        <v>620203.5688459591</v>
+        <v>620190.9776712308</v>
       </c>
       <c r="H4" t="n">
-        <v>621966.2084079118</v>
+        <v>621952.8827629021</v>
       </c>
       <c r="I4" t="n">
-        <v>620074.1902562872</v>
+        <v>620060.8423546022</v>
       </c>
       <c r="J4" t="n">
-        <v>545700.3943811483</v>
+        <v>545687.7141797191</v>
       </c>
       <c r="K4" t="n">
-        <v>546852.8520215957</v>
+        <v>546843.1542146424</v>
       </c>
       <c r="L4" t="n">
-        <v>619081.6392964619</v>
+        <v>619071.9414895086</v>
       </c>
       <c r="M4" t="n">
-        <v>617043.0502748413</v>
+        <v>617033.5305212894</v>
       </c>
       <c r="N4" t="n">
-        <v>614819.7349721636</v>
+        <v>614810.2152186118</v>
       </c>
       <c r="O4" t="n">
-        <v>461312.8081018848</v>
+        <v>461303.288348333</v>
       </c>
       <c r="P4" t="n">
-        <v>404637.9167037315</v>
+        <v>404629.1314204611</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>341747.9822777616</v>
+        <v>341757.4130046127</v>
       </c>
       <c r="C6" t="n">
-        <v>546523.0381322898</v>
+        <v>546535.4512536167</v>
       </c>
       <c r="D6" t="n">
-        <v>596520.6328006889</v>
+        <v>596533.0459220159</v>
       </c>
       <c r="E6" t="n">
-        <v>305696.7919404489</v>
+        <v>305709.3831151769</v>
       </c>
       <c r="F6" t="n">
-        <v>552659.4560320511</v>
+        <v>552672.0472067787</v>
       </c>
       <c r="G6" t="n">
-        <v>523300.6809006053</v>
+        <v>523313.2720753337</v>
       </c>
       <c r="H6" t="n">
-        <v>597461.5659097561</v>
+        <v>597474.8915547661</v>
       </c>
       <c r="I6" t="n">
-        <v>610873.4185333803</v>
+        <v>610886.766435066</v>
       </c>
       <c r="J6" t="n">
-        <v>339763.0095241616</v>
+        <v>339775.6897255905</v>
       </c>
       <c r="K6" t="n">
-        <v>529182.6896980313</v>
+        <v>529192.3875049846</v>
       </c>
       <c r="L6" t="n">
-        <v>429739.6362305665</v>
+        <v>429749.3340375198</v>
       </c>
       <c r="M6" t="n">
-        <v>613331.5492521869</v>
+        <v>613341.0690057389</v>
       </c>
       <c r="N6" t="n">
-        <v>618754.8645548646</v>
+        <v>618764.3843084162</v>
       </c>
       <c r="O6" t="n">
-        <v>504002.1905014555</v>
+        <v>504011.7102550071</v>
       </c>
       <c r="P6" t="n">
-        <v>459536.5885318899</v>
+        <v>459545.3738151601</v>
       </c>
     </row>
   </sheetData>
@@ -26984,7 +26984,7 @@
         <v>303</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>100</v>
@@ -27008,7 +27008,7 @@
         <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O2" t="n">
         <v>-0</v>
@@ -27524,16 +27524,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>169.749824043404</v>
       </c>
       <c r="G3" t="n">
-        <v>325.3867811580462</v>
+        <v>141.3867811580462</v>
       </c>
       <c r="H3" t="n">
         <v>328.7612192618928</v>
       </c>
       <c r="I3" t="n">
-        <v>20.98110287248061</v>
+        <v>204.9811028724806</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,16 +27557,16 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>128.0504349018003</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>404</v>
       </c>
       <c r="S3" t="n">
-        <v>276.0117358136679</v>
+        <v>404</v>
       </c>
       <c r="T3" t="n">
-        <v>233.987327150969</v>
+        <v>403.93591616091</v>
       </c>
       <c r="U3" t="n">
         <v>400.1871522130169</v>
@@ -27609,19 +27609,19 @@
         <v>244.748135136612</v>
       </c>
       <c r="H4" t="n">
-        <v>404</v>
+        <v>226.1417490524383</v>
       </c>
       <c r="I4" t="n">
-        <v>167.739816275856</v>
+        <v>351.739816275856</v>
       </c>
       <c r="J4" t="n">
-        <v>14.36029309820285</v>
+        <v>198.3602930982029</v>
       </c>
       <c r="K4" t="n">
         <v>404</v>
       </c>
       <c r="L4" t="n">
-        <v>399.4843654995094</v>
+        <v>404</v>
       </c>
       <c r="M4" t="n">
         <v>404</v>
@@ -27642,7 +27642,7 @@
         <v>404</v>
       </c>
       <c r="S4" t="n">
-        <v>404</v>
+        <v>357.2195780635112</v>
       </c>
       <c r="T4" t="n">
         <v>208.7609599488807</v>
@@ -27654,13 +27654,13 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
-        <v>404</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
         <v>404</v>
       </c>
       <c r="Y4" t="n">
-        <v>287.4653528494624</v>
+        <v>317.2155813943127</v>
       </c>
     </row>
     <row r="5">
@@ -27679,7 +27679,7 @@
         <v>405</v>
       </c>
       <c r="E5" t="n">
-        <v>404.3632896068687</v>
+        <v>404.3632896068686</v>
       </c>
       <c r="F5" t="n">
         <v>404.8896287080118</v>
@@ -27758,10 +27758,10 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>114.3242467686489</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>21.63624233787687</v>
       </c>
       <c r="G6" t="n">
         <v>325.3867811580462</v>
@@ -27794,19 +27794,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>128.0504349018003</v>
       </c>
       <c r="R6" t="n">
-        <v>405</v>
+        <v>207.3720614433227</v>
       </c>
       <c r="S6" t="n">
-        <v>162.0863817055272</v>
+        <v>142.0117358136679</v>
       </c>
       <c r="T6" t="n">
         <v>403.93591616091</v>
       </c>
       <c r="U6" t="n">
-        <v>82.18715221301693</v>
+        <v>400.1871522130169</v>
       </c>
       <c r="V6" t="n">
         <v>405</v>
@@ -27818,7 +27818,7 @@
         <v>405</v>
       </c>
       <c r="Y6" t="n">
-        <v>81.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="7">
@@ -27828,7 +27828,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>405</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
         <v>405</v>
@@ -27837,28 +27837,28 @@
         <v>285.5362180555555</v>
       </c>
       <c r="E7" t="n">
-        <v>280.9809048369565</v>
+        <v>405</v>
       </c>
       <c r="F7" t="n">
         <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
-        <v>405</v>
+        <v>244.748135136612</v>
       </c>
       <c r="H7" t="n">
-        <v>405</v>
+        <v>226.1417490524383</v>
       </c>
       <c r="I7" t="n">
-        <v>405</v>
+        <v>167.739816275856</v>
       </c>
       <c r="J7" t="n">
-        <v>14.36029309820285</v>
+        <v>182.4642998654427</v>
       </c>
       <c r="K7" t="n">
-        <v>405</v>
+        <v>254.161429538848</v>
       </c>
       <c r="L7" t="n">
-        <v>405</v>
+        <v>379.5794970102382</v>
       </c>
       <c r="M7" t="n">
         <v>405</v>
@@ -27879,19 +27879,19 @@
         <v>405</v>
       </c>
       <c r="S7" t="n">
-        <v>405</v>
+        <v>357.2195780635112</v>
       </c>
       <c r="T7" t="n">
         <v>405</v>
       </c>
       <c r="U7" t="n">
-        <v>163.2839872899398</v>
+        <v>405</v>
       </c>
       <c r="V7" t="n">
-        <v>199.1703102162162</v>
+        <v>405</v>
       </c>
       <c r="W7" t="n">
-        <v>226.3728098387097</v>
+        <v>405</v>
       </c>
       <c r="X7" t="n">
         <v>247.4436454301076</v>
@@ -27986,16 +27986,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384.5565566463266</v>
+        <v>66.55655664632661</v>
       </c>
       <c r="C9" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>294.9736337014295</v>
       </c>
       <c r="E9" t="n">
-        <v>24.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
         <v>339.6362423378769</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>128.0504349018003</v>
       </c>
       <c r="R9" t="n">
         <v>405</v>
@@ -28052,10 +28052,10 @@
         <v>405</v>
       </c>
       <c r="X9" t="n">
-        <v>162.0863817055272</v>
+        <v>405</v>
       </c>
       <c r="Y9" t="n">
-        <v>399.3913927661343</v>
+        <v>81.39139276613435</v>
       </c>
     </row>
     <row r="10">
@@ -28068,7 +28068,7 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C10" t="n">
-        <v>357.3669457373174</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D10" t="n">
         <v>405</v>
@@ -28077,19 +28077,19 @@
         <v>405</v>
       </c>
       <c r="F10" t="n">
-        <v>405</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G10" t="n">
         <v>405</v>
       </c>
       <c r="H10" t="n">
-        <v>405</v>
+        <v>226.1417490524383</v>
       </c>
       <c r="I10" t="n">
-        <v>405</v>
+        <v>371.3411614356891</v>
       </c>
       <c r="J10" t="n">
-        <v>14.36029309820285</v>
+        <v>332.3602930982029</v>
       </c>
       <c r="K10" t="n">
         <v>405</v>
@@ -28116,7 +28116,7 @@
         <v>405</v>
       </c>
       <c r="S10" t="n">
-        <v>405</v>
+        <v>357.2195780635112</v>
       </c>
       <c r="T10" t="n">
         <v>208.7609599488807</v>
@@ -28131,7 +28131,7 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
-        <v>247.4436454301076</v>
+        <v>405</v>
       </c>
       <c r="Y10" t="n">
         <v>287.4653528494624</v>
@@ -28268,7 +28268,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>128.0504349018159</v>
+        <v>128.0504349018003</v>
       </c>
       <c r="R12" t="n">
         <v>308</v>
@@ -28308,7 +28308,7 @@
         <v>308</v>
       </c>
       <c r="D13" t="n">
-        <v>298.8740701859106</v>
+        <v>308</v>
       </c>
       <c r="E13" t="n">
         <v>308</v>
@@ -28329,7 +28329,7 @@
         <v>308</v>
       </c>
       <c r="K13" t="n">
-        <v>308</v>
+        <v>298.8740701859106</v>
       </c>
       <c r="L13" t="n">
         <v>308</v>
@@ -28566,7 +28566,7 @@
         <v>308</v>
       </c>
       <c r="K16" t="n">
-        <v>308</v>
+        <v>298.8740701859106</v>
       </c>
       <c r="L16" t="n">
         <v>308</v>
@@ -28596,7 +28596,7 @@
         <v>308</v>
       </c>
       <c r="U16" t="n">
-        <v>298.8740701859106</v>
+        <v>308</v>
       </c>
       <c r="V16" t="n">
         <v>308</v>
@@ -28697,25 +28697,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>58.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C18" t="n">
-        <v>35.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D18" t="n">
-        <v>347.9376868977026</v>
+        <v>263.9408719496474</v>
       </c>
       <c r="E18" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F18" t="n">
-        <v>339.6362423378769</v>
+        <v>13.63624233787687</v>
       </c>
       <c r="G18" t="n">
-        <v>325.3867811580462</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>273.75076606562</v>
+        <v>328.7612192618928</v>
       </c>
       <c r="I18" t="n">
         <v>204.9811028724806</v>
@@ -28760,13 +28760,13 @@
         <v>404</v>
       </c>
       <c r="W18" t="n">
-        <v>404</v>
+        <v>106.3731429098285</v>
       </c>
       <c r="X18" t="n">
         <v>404</v>
       </c>
       <c r="Y18" t="n">
-        <v>73.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="19">
@@ -28776,13 +28776,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>404</v>
+        <v>358.5514574131262</v>
       </c>
       <c r="C19" t="n">
         <v>272.7252466480447</v>
       </c>
       <c r="D19" t="n">
-        <v>285.5362180555555</v>
+        <v>404</v>
       </c>
       <c r="E19" t="n">
         <v>280.9809048369565</v>
@@ -28794,7 +28794,7 @@
         <v>404</v>
       </c>
       <c r="H19" t="n">
-        <v>226.1417490524383</v>
+        <v>404</v>
       </c>
       <c r="I19" t="n">
         <v>167.739816275856</v>
@@ -28803,10 +28803,10 @@
         <v>14.36029309820285</v>
       </c>
       <c r="K19" t="n">
-        <v>254.161429538848</v>
+        <v>404</v>
       </c>
       <c r="L19" t="n">
-        <v>379.5794970102382</v>
+        <v>404</v>
       </c>
       <c r="M19" t="n">
         <v>404</v>
@@ -28827,7 +28827,7 @@
         <v>404</v>
       </c>
       <c r="S19" t="n">
-        <v>404</v>
+        <v>357.2195780635112</v>
       </c>
       <c r="T19" t="n">
         <v>404</v>
@@ -28836,10 +28836,10 @@
         <v>404</v>
       </c>
       <c r="V19" t="n">
-        <v>404</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W19" t="n">
-        <v>399.8952618744834</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X19" t="n">
         <v>247.4436454301076</v>
@@ -28943,16 +28943,16 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E21" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>325.3867811580462</v>
+        <v>154.542447868807</v>
       </c>
       <c r="H21" t="n">
-        <v>320.9241675816012</v>
+        <v>328.7612192618928</v>
       </c>
       <c r="I21" t="n">
         <v>204.9811028724806</v>
@@ -28979,13 +28979,13 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>128.0504349018003</v>
       </c>
       <c r="R21" t="n">
         <v>403</v>
       </c>
       <c r="S21" t="n">
-        <v>403</v>
+        <v>101.0117358136655</v>
       </c>
       <c r="T21" t="n">
         <v>403</v>
@@ -28994,13 +28994,13 @@
         <v>400.1871522130169</v>
       </c>
       <c r="V21" t="n">
-        <v>55.51066719151774</v>
+        <v>403</v>
       </c>
       <c r="W21" t="n">
-        <v>73.3731429098261</v>
+        <v>403</v>
       </c>
       <c r="X21" t="n">
-        <v>60.86273944538513</v>
+        <v>403</v>
       </c>
       <c r="Y21" t="n">
         <v>399.3913927661343</v>
@@ -29025,13 +29025,13 @@
         <v>280.9809048369565</v>
       </c>
       <c r="F22" t="n">
-        <v>403</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G22" t="n">
         <v>403</v>
       </c>
       <c r="H22" t="n">
-        <v>403</v>
+        <v>226.1417490524383</v>
       </c>
       <c r="I22" t="n">
         <v>403</v>
@@ -29064,19 +29064,19 @@
         <v>403</v>
       </c>
       <c r="S22" t="n">
+        <v>357.2195780635112</v>
+      </c>
+      <c r="T22" t="n">
+        <v>282.6990977530156</v>
+      </c>
+      <c r="U22" t="n">
         <v>403</v>
       </c>
-      <c r="T22" t="n">
+      <c r="V22" t="n">
         <v>403</v>
       </c>
-      <c r="U22" t="n">
-        <v>311.900160781781</v>
-      </c>
-      <c r="V22" t="n">
-        <v>199.1703102162162</v>
-      </c>
       <c r="W22" t="n">
-        <v>226.3728098387097</v>
+        <v>403</v>
       </c>
       <c r="X22" t="n">
         <v>247.4436454301076</v>
@@ -29174,13 +29174,13 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C24" t="n">
-        <v>3.453078367705189</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>339.6362423378769</v>
@@ -29192,7 +29192,7 @@
         <v>328.7612192618928</v>
       </c>
       <c r="I24" t="n">
-        <v>204.9811028724806</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -29216,10 +29216,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>79.69661767556647</v>
       </c>
       <c r="R24" t="n">
-        <v>403</v>
+        <v>165.3720614433102</v>
       </c>
       <c r="S24" t="n">
         <v>403</v>
@@ -29259,7 +29259,7 @@
         <v>285.5362180555555</v>
       </c>
       <c r="E25" t="n">
-        <v>280.9809048369565</v>
+        <v>403</v>
       </c>
       <c r="F25" t="n">
         <v>274.3828559677419</v>
@@ -29271,13 +29271,13 @@
         <v>403</v>
       </c>
       <c r="I25" t="n">
-        <v>167.739816275856</v>
+        <v>403</v>
       </c>
       <c r="J25" t="n">
         <v>14.36029309820285</v>
       </c>
       <c r="K25" t="n">
-        <v>403</v>
+        <v>254.161429538848</v>
       </c>
       <c r="L25" t="n">
         <v>403</v>
@@ -29301,22 +29301,22 @@
         <v>403</v>
       </c>
       <c r="S25" t="n">
-        <v>357.2195780635112</v>
+        <v>390.4848184428371</v>
       </c>
       <c r="T25" t="n">
+        <v>208.7609599488807</v>
+      </c>
+      <c r="U25" t="n">
         <v>403</v>
       </c>
-      <c r="U25" t="n">
-        <v>402.1935735403507</v>
-      </c>
       <c r="V25" t="n">
-        <v>403</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W25" t="n">
         <v>226.3728098387097</v>
       </c>
       <c r="X25" t="n">
-        <v>247.4436454301076</v>
+        <v>403</v>
       </c>
       <c r="Y25" t="n">
         <v>403</v>
@@ -29724,13 +29724,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>345</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C31" t="n">
         <v>345</v>
       </c>
       <c r="D31" t="n">
-        <v>345</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E31" t="n">
         <v>345</v>
@@ -29739,19 +29739,19 @@
         <v>345</v>
       </c>
       <c r="G31" t="n">
-        <v>345</v>
+        <v>244.748135136612</v>
       </c>
       <c r="H31" t="n">
         <v>226.1417490524383</v>
       </c>
       <c r="I31" t="n">
-        <v>167.739816275856</v>
+        <v>313.8320212971356</v>
       </c>
       <c r="J31" t="n">
-        <v>14.36029309820285</v>
+        <v>210.3602930982031</v>
       </c>
       <c r="K31" t="n">
-        <v>254.161429538848</v>
+        <v>345</v>
       </c>
       <c r="L31" t="n">
         <v>345</v>
@@ -29778,22 +29778,22 @@
         <v>345</v>
       </c>
       <c r="T31" t="n">
-        <v>208.7609599488807</v>
+        <v>345</v>
       </c>
       <c r="U31" t="n">
         <v>150.9422601269169</v>
       </c>
       <c r="V31" t="n">
-        <v>277.0200873972932</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W31" t="n">
-        <v>345</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X31" t="n">
-        <v>345</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y31" t="n">
-        <v>345</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="32">
@@ -29888,7 +29888,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D33" t="n">
-        <v>347.9376868977026</v>
+        <v>151.9376868977022</v>
       </c>
       <c r="E33" t="n">
         <v>342.6720972219126</v>
@@ -29927,7 +29927,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>128.0504349018003</v>
       </c>
       <c r="R33" t="n">
         <v>476</v>
@@ -29939,19 +29939,19 @@
         <v>403.93591616091</v>
       </c>
       <c r="U33" t="n">
-        <v>400.1871522130169</v>
+        <v>204.1871522130166</v>
       </c>
       <c r="V33" t="n">
-        <v>414.5106671915202</v>
+        <v>291.2459286348441</v>
       </c>
       <c r="W33" t="n">
-        <v>241.1588392549516</v>
+        <v>236.3731429098281</v>
       </c>
       <c r="X33" t="n">
-        <v>223.8627394453875</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y33" t="n">
-        <v>203.3913927661343</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="34">
@@ -29964,7 +29964,7 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C34" t="n">
-        <v>272.7252466480447</v>
+        <v>468.7252466480451</v>
       </c>
       <c r="D34" t="n">
         <v>285.5362180555555</v>
@@ -29976,25 +29976,25 @@
         <v>274.3828559677419</v>
       </c>
       <c r="G34" t="n">
-        <v>440.748135136612</v>
+        <v>244.748135136612</v>
       </c>
       <c r="H34" t="n">
         <v>226.1417490524383</v>
       </c>
       <c r="I34" t="n">
-        <v>238.6027443414335</v>
+        <v>214.5162072890592</v>
       </c>
       <c r="J34" t="n">
         <v>14.36029309820285</v>
       </c>
       <c r="K34" t="n">
-        <v>450.161429538848</v>
+        <v>450.1614295388484</v>
       </c>
       <c r="L34" t="n">
+        <v>379.5794970102382</v>
+      </c>
+      <c r="M34" t="n">
         <v>476</v>
-      </c>
-      <c r="M34" t="n">
-        <v>474.2733818943532</v>
       </c>
       <c r="N34" t="n">
         <v>476</v>
@@ -30012,13 +30012,13 @@
         <v>476</v>
       </c>
       <c r="S34" t="n">
-        <v>357.2195780635112</v>
+        <v>476</v>
       </c>
       <c r="T34" t="n">
         <v>208.7609599488807</v>
       </c>
       <c r="U34" t="n">
-        <v>346.9422601269169</v>
+        <v>346.9422601269173</v>
       </c>
       <c r="V34" t="n">
         <v>199.1703102162162</v>
@@ -30119,7 +30119,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>204.3886529914497</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C36" t="n">
         <v>361.0999124455193</v>
@@ -30128,10 +30128,10 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>342.6720972219126</v>
+        <v>154.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>339.6362423378769</v>
+        <v>219.4179037811996</v>
       </c>
       <c r="G36" t="n">
         <v>325.3867811580462</v>
@@ -30164,7 +30164,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>128.0504349018003</v>
       </c>
       <c r="R36" t="n">
         <v>480</v>
@@ -30179,7 +30179,7 @@
         <v>400.1871522130169</v>
       </c>
       <c r="V36" t="n">
-        <v>226.5106671915202</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W36" t="n">
         <v>432.3731429098285</v>
@@ -30188,7 +30188,7 @@
         <v>231.8627394453875</v>
       </c>
       <c r="Y36" t="n">
-        <v>399.3913927661343</v>
+        <v>211.3913927661343</v>
       </c>
     </row>
     <row r="37">
@@ -30198,7 +30198,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>287.1138003370787</v>
+        <v>475.1138003370787</v>
       </c>
       <c r="C37" t="n">
         <v>272.7252466480447</v>
@@ -30210,13 +30210,13 @@
         <v>280.9809048369565</v>
       </c>
       <c r="F37" t="n">
-        <v>462.3828559677419</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G37" t="n">
-        <v>432.748135136612</v>
+        <v>407.4630527749532</v>
       </c>
       <c r="H37" t="n">
-        <v>288.4361637010177</v>
+        <v>226.1417490524383</v>
       </c>
       <c r="I37" t="n">
         <v>167.739816275856</v>
@@ -30225,10 +30225,10 @@
         <v>14.36029309820285</v>
       </c>
       <c r="K37" t="n">
-        <v>442.161429538848</v>
+        <v>254.161429538848</v>
       </c>
       <c r="L37" t="n">
-        <v>480</v>
+        <v>379.5794970102382</v>
       </c>
       <c r="M37" t="n">
         <v>474.2733818943532</v>
@@ -30261,10 +30261,10 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W37" t="n">
-        <v>226.3728098387097</v>
+        <v>414.3728098387097</v>
       </c>
       <c r="X37" t="n">
-        <v>247.4436454301076</v>
+        <v>435.4436454301076</v>
       </c>
       <c r="Y37" t="n">
         <v>287.4653528494624</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>206.6548096186206</v>
+        <v>206.6548096186207</v>
       </c>
       <c r="S38" t="n">
         <v>479.8244492093581</v>
@@ -30359,19 +30359,19 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C39" t="n">
-        <v>361.0999124455193</v>
+        <v>240.8815738888421</v>
       </c>
       <c r="D39" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>162.5041935670357</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>339.6362423378769</v>
+        <v>151.6362423378769</v>
       </c>
       <c r="G39" t="n">
-        <v>325.3867811580462</v>
+        <v>137.3867811580462</v>
       </c>
       <c r="H39" t="n">
         <v>328.7612192618928</v>
@@ -30401,7 +30401,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>128.0504349018003</v>
       </c>
       <c r="R39" t="n">
         <v>480</v>
@@ -30425,7 +30425,7 @@
         <v>419.8627394453875</v>
       </c>
       <c r="Y39" t="n">
-        <v>211.3913927661343</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="40">
@@ -30438,10 +30438,10 @@
         <v>475.1138003370787</v>
       </c>
       <c r="C40" t="n">
-        <v>272.7252466480447</v>
+        <v>460.7252466480447</v>
       </c>
       <c r="D40" t="n">
-        <v>473.5362180555555</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E40" t="n">
         <v>280.9809048369565</v>
@@ -30450,7 +30450,7 @@
         <v>274.3828559677419</v>
       </c>
       <c r="G40" t="n">
-        <v>244.748135136612</v>
+        <v>407.463052774953</v>
       </c>
       <c r="H40" t="n">
         <v>226.1417490524383</v>
@@ -30462,10 +30462,10 @@
         <v>14.36029309820285</v>
       </c>
       <c r="K40" t="n">
-        <v>381.6754222509385</v>
+        <v>254.161429538848</v>
       </c>
       <c r="L40" t="n">
-        <v>480</v>
+        <v>379.5794970102382</v>
       </c>
       <c r="M40" t="n">
         <v>474.2733818943532</v>
@@ -30486,7 +30486,7 @@
         <v>480</v>
       </c>
       <c r="S40" t="n">
-        <v>480</v>
+        <v>357.2195780635112</v>
       </c>
       <c r="T40" t="n">
         <v>208.7609599488807</v>
@@ -30498,7 +30498,7 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W40" t="n">
-        <v>226.3728098387097</v>
+        <v>414.3728098387097</v>
       </c>
       <c r="X40" t="n">
         <v>247.4436454301076</v>
@@ -34743,28 +34743,28 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
+        <v>20.91395857903028</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.86498492462312</v>
+      </c>
+      <c r="L2" t="n">
         <v>184</v>
       </c>
-      <c r="K2" t="n">
-        <v>83.86498492462314</v>
-      </c>
-      <c r="L2" t="n">
-        <v>104.0419296482412</v>
-      </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="N2" t="n">
-        <v>37.30197311510387</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>40.83617062691258</v>
+        <v>71.78671306200322</v>
       </c>
       <c r="P2" t="n">
-        <v>94.52059825077588</v>
+        <v>184</v>
       </c>
       <c r="Q2" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34822,25 +34822,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>158.5361911433361</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>184</v>
       </c>
       <c r="M3" t="n">
-        <v>21.00278166238429</v>
+        <v>176.3300421645043</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="P3" t="n">
-        <v>181.0266837599362</v>
+        <v>0.2356144011523703</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -34895,19 +34895,19 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>177.8582509475617</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="K4" t="n">
         <v>149.838570461152</v>
       </c>
       <c r="L4" t="n">
-        <v>19.90486848927122</v>
+        <v>24.42050298976181</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34928,7 +34928,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>46.78042193648884</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -34940,13 +34940,13 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>177.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>156.5563545698924</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>29.75022854485036</v>
       </c>
     </row>
     <row r="5">
@@ -34965,7 +34965,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-8.310670694506807e-14</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -34983,16 +34983,16 @@
         <v>318</v>
       </c>
       <c r="K5" t="n">
-        <v>83.86498492462312</v>
+        <v>169.7947462738268</v>
       </c>
       <c r="L5" t="n">
-        <v>104.0419296482412</v>
+        <v>318</v>
       </c>
       <c r="M5" t="n">
         <v>318</v>
       </c>
       <c r="N5" t="n">
-        <v>299.8878317009625</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>40.83617062691258</v>
@@ -35071,13 +35071,13 @@
         <v>176.3300421645043</v>
       </c>
       <c r="N6" t="n">
-        <v>226.3721727501643</v>
+        <v>177.1925924995509</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>131.8471035093229</v>
+        <v>181.0266837599362</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -35114,7 +35114,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>117.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
         <v>132.2747533519553</v>
@@ -35123,28 +35123,28 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>124.0190951630435</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>160.251864863388</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>178.8582509475617</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>237.260183724144</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>168.1040067672399</v>
       </c>
       <c r="K7" t="n">
-        <v>150.838570461152</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>25.42050298976181</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35165,19 +35165,19 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>47.78042193648883</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>196.2390400511193</v>
       </c>
       <c r="U7" t="n">
-        <v>12.34172716302284</v>
+        <v>254.0577398730831</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>205.8296897837838</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>178.6271901612903</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -35217,28 +35217,28 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>299.8878317009625</v>
+        <v>20.91395857903028</v>
       </c>
       <c r="K8" t="n">
         <v>83.86498492462312</v>
       </c>
       <c r="L8" t="n">
-        <v>104.0419296482412</v>
+        <v>105.851973397086</v>
       </c>
       <c r="M8" t="n">
-        <v>318</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>318</v>
       </c>
       <c r="O8" t="n">
-        <v>40.83617062691258</v>
+        <v>318</v>
       </c>
       <c r="P8" t="n">
         <v>94.52059825077588</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>318</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35299,16 +35299,16 @@
         <v>158.5361911433361</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>248.0660055841875</v>
       </c>
       <c r="L9" t="n">
-        <v>198.8864253335743</v>
+        <v>177.192592499551</v>
       </c>
       <c r="M9" t="n">
         <v>176.3300421645043</v>
       </c>
       <c r="N9" t="n">
-        <v>226.3721727501643</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>318</v>
@@ -35354,7 +35354,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>84.64169908927272</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>119.4637819444445</v>
@@ -35363,19 +35363,19 @@
         <v>124.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>130.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>160.251864863388</v>
       </c>
       <c r="H10" t="n">
-        <v>178.8582509475617</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>237.260183724144</v>
+        <v>203.601345159833</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>318</v>
       </c>
       <c r="K10" t="n">
         <v>150.838570461152</v>
@@ -35402,7 +35402,7 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>47.78042193648883</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -35417,7 +35417,7 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>157.5563545698924</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -35454,25 +35454,25 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
+        <v>20.91395857903028</v>
+      </c>
+      <c r="K11" t="n">
+        <v>83.86498492462313</v>
+      </c>
+      <c r="L11" t="n">
+        <v>208.0493393246294</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>326</v>
       </c>
-      <c r="K11" t="n">
-        <v>326.0000000000001</v>
-      </c>
-      <c r="L11" t="n">
-        <v>177.4715139505944</v>
-      </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>326</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>40.83617062691258</v>
-      </c>
       <c r="P11" t="n">
-        <v>94.52059825077588</v>
+        <v>326</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -35536,13 +35536,13 @@
         <v>158.5361911433361</v>
       </c>
       <c r="K12" t="n">
-        <v>248.0660055841875</v>
+        <v>73.50689251738274</v>
       </c>
       <c r="L12" t="n">
-        <v>156.1375285286272</v>
+        <v>326</v>
       </c>
       <c r="M12" t="n">
-        <v>176.3300421645043</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>226.3721727501643</v>
@@ -35551,7 +35551,7 @@
         <v>325.3863426574634</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>181.0266837599362</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -35594,7 +35594,7 @@
         <v>35.27475335195533</v>
       </c>
       <c r="D13" t="n">
-        <v>13.3378521303551</v>
+        <v>22.46378194444452</v>
       </c>
       <c r="E13" t="n">
         <v>27.01909516304346</v>
@@ -35615,7 +35615,7 @@
         <v>293.6397069017971</v>
       </c>
       <c r="K13" t="n">
-        <v>53.83857046115203</v>
+        <v>44.71264064706261</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -35694,25 +35694,25 @@
         <v>20.91395857903028</v>
       </c>
       <c r="K14" t="n">
-        <v>83.86498492462313</v>
+        <v>326</v>
       </c>
       <c r="L14" t="n">
-        <v>104.0419296482412</v>
+        <v>326</v>
       </c>
       <c r="M14" t="n">
-        <v>294.6506407986997</v>
+        <v>326</v>
       </c>
       <c r="N14" t="n">
-        <v>326</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>40.83617062691258</v>
       </c>
       <c r="P14" t="n">
-        <v>94.52059825077588</v>
+        <v>251.07815362234</v>
       </c>
       <c r="Q14" t="n">
-        <v>326</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35773,7 +35773,7 @@
         <v>158.5361911433361</v>
       </c>
       <c r="K15" t="n">
-        <v>248.0660055841875</v>
+        <v>123.5490231030427</v>
       </c>
       <c r="L15" t="n">
         <v>326</v>
@@ -35782,13 +35782,13 @@
         <v>176.3300421645043</v>
       </c>
       <c r="N15" t="n">
-        <v>56.5097012787915</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>325.3863426574634</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>181.0266837599362</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -35840,7 +35840,7 @@
         <v>33.61714403225807</v>
       </c>
       <c r="G16" t="n">
-        <v>63.25186486338799</v>
+        <v>63.251864863388</v>
       </c>
       <c r="H16" t="n">
         <v>81.85825094756171</v>
@@ -35852,7 +35852,7 @@
         <v>293.6397069017971</v>
       </c>
       <c r="K16" t="n">
-        <v>53.83857046115202</v>
+        <v>44.71264064706261</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -35882,7 +35882,7 @@
         <v>99.23904005111933</v>
       </c>
       <c r="U16" t="n">
-        <v>147.9318100589936</v>
+        <v>157.0577398730831</v>
       </c>
       <c r="V16" t="n">
         <v>108.8296897837838</v>
@@ -35928,19 +35928,19 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
+        <v>177.4715139505944</v>
+      </c>
+      <c r="K17" t="n">
         <v>326</v>
       </c>
-      <c r="K17" t="n">
-        <v>83.86498492462312</v>
-      </c>
       <c r="L17" t="n">
-        <v>104.0419296482412</v>
+        <v>326</v>
       </c>
       <c r="M17" t="n">
-        <v>315.56459937773</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>326</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>40.83617062691258</v>
@@ -35949,7 +35949,7 @@
         <v>94.52059825077588</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>326</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36007,13 +36007,13 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>158.5361911433361</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>248.0660055841875</v>
+        <v>55.71304149621457</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>326</v>
       </c>
       <c r="M18" t="n">
         <v>176.3300421645043</v>
@@ -36022,7 +36022,7 @@
         <v>226.3721727501643</v>
       </c>
       <c r="O18" t="n">
-        <v>300.4971874261543</v>
+        <v>325.3863426574634</v>
       </c>
       <c r="P18" t="n">
         <v>181.0266837599362</v>
@@ -36062,13 +36062,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>116.8861996629213</v>
+        <v>71.43765707604759</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>118.4637819444445</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -36080,7 +36080,7 @@
         <v>159.251864863388</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>177.8582509475617</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -36089,10 +36089,10 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>149.838570461152</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>24.42050298976181</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -36113,7 +36113,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>46.78042193648883</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>195.2390400511193</v>
@@ -36122,10 +36122,10 @@
         <v>253.0577398730831</v>
       </c>
       <c r="V19" t="n">
-        <v>204.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>173.5224520357737</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -36165,28 +36165,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>21.23126604438952</v>
+        <v>20.91395857903028</v>
       </c>
       <c r="K20" t="n">
-        <v>83.86498492462312</v>
+        <v>359</v>
       </c>
       <c r="L20" t="n">
-        <v>104.0419296482412</v>
+        <v>359</v>
       </c>
       <c r="M20" t="n">
-        <v>359.0000000000024</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>359.0000000000024</v>
+        <v>359.000000000002</v>
       </c>
       <c r="O20" t="n">
         <v>40.83617062691258</v>
       </c>
       <c r="P20" t="n">
-        <v>94.52059825077588</v>
+        <v>282.7448202890047</v>
       </c>
       <c r="Q20" t="n">
-        <v>359.0000000000024</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36244,10 +36244,10 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>158.5361911433361</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>3.159500161424198</v>
+        <v>248.0660055841875</v>
       </c>
       <c r="L21" t="n">
         <v>350.684016858121</v>
@@ -36262,7 +36262,7 @@
         <v>325.3863426574634</v>
       </c>
       <c r="P21" t="n">
-        <v>181.0266837599362</v>
+        <v>94.65636948050911</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -36311,13 +36311,13 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>128.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
         <v>158.251864863388</v>
       </c>
       <c r="H22" t="n">
-        <v>176.8582509475617</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>235.260183724144</v>
@@ -36350,19 +36350,19 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>45.78042193648884</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>194.2390400511193</v>
+        <v>73.93813780413493</v>
       </c>
       <c r="U22" t="n">
-        <v>160.957900654864</v>
+        <v>252.0577398730831</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>203.8296897837838</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>176.6271901612903</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -36402,28 +36402,28 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>20.91395857903028</v>
+        <v>360.0000000000065</v>
       </c>
       <c r="K23" t="n">
-        <v>360</v>
+        <v>83.86498492462312</v>
       </c>
       <c r="L23" t="n">
         <v>104.0419296482412</v>
       </c>
       <c r="M23" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>85.14188834958543</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>40.83617062691258</v>
+        <v>157.5476308816615</v>
       </c>
       <c r="P23" t="n">
-        <v>94.52059825077588</v>
+        <v>360.0000000000065</v>
       </c>
       <c r="Q23" t="n">
-        <v>360</v>
+        <v>360.0000000000065</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36481,22 +36481,22 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>158.5361911433361</v>
       </c>
       <c r="K24" t="n">
-        <v>165.6552872643562</v>
+        <v>248.0660055841875</v>
       </c>
       <c r="L24" t="n">
         <v>350.684016858121</v>
       </c>
       <c r="M24" t="n">
-        <v>176.3300421645043</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>226.3721727501643</v>
       </c>
       <c r="O24" t="n">
-        <v>325.3863426574634</v>
+        <v>260.7694753588003</v>
       </c>
       <c r="P24" t="n">
         <v>181.0266837599362</v>
@@ -36545,7 +36545,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>122.0190951630435</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -36557,13 +36557,13 @@
         <v>176.8582509475617</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>235.260183724144</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>148.838570461152</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>23.42050298976181</v>
@@ -36587,22 +36587,22 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>33.26524037932589</v>
       </c>
       <c r="T25" t="n">
-        <v>194.2390400511193</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>251.2513134134337</v>
+        <v>252.0577398730831</v>
       </c>
       <c r="V25" t="n">
-        <v>203.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>155.5563545698924</v>
       </c>
       <c r="Y25" t="n">
         <v>115.5346471505376</v>
@@ -36639,19 +36639,19 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>330</v>
+        <v>20.91395857903028</v>
       </c>
       <c r="K26" t="n">
         <v>83.86498492462312</v>
       </c>
       <c r="L26" t="n">
-        <v>104.0419296482413</v>
+        <v>330</v>
       </c>
       <c r="M26" t="n">
-        <v>330</v>
+        <v>330.0000000000019</v>
       </c>
       <c r="N26" t="n">
-        <v>323.402983216114</v>
+        <v>76.5309542853211</v>
       </c>
       <c r="O26" t="n">
         <v>40.83617062691258</v>
@@ -36660,7 +36660,7 @@
         <v>94.52059825077588</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>330.0000000000019</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36718,22 +36718,22 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>158.5361911433361</v>
       </c>
       <c r="K27" t="n">
         <v>248.0660055841875</v>
       </c>
       <c r="L27" t="n">
-        <v>149.4854197504109</v>
+        <v>330.0000000000019</v>
       </c>
       <c r="M27" t="n">
         <v>176.3300421645043</v>
       </c>
       <c r="N27" t="n">
-        <v>226.3721727501643</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>325.3863426574634</v>
+        <v>212.7077440147006</v>
       </c>
       <c r="P27" t="n">
         <v>181.0266837599362</v>
@@ -36876,28 +36876,28 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>20.91395857903028</v>
+        <v>196.0000000000003</v>
       </c>
       <c r="K29" t="n">
-        <v>83.86498492462312</v>
+        <v>83.86498492462309</v>
       </c>
       <c r="L29" t="n">
         <v>104.0419296482412</v>
       </c>
       <c r="M29" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>40.83617062691258</v>
       </c>
       <c r="P29" t="n">
-        <v>94.52059825077588</v>
+        <v>155.3377228810307</v>
       </c>
       <c r="Q29" t="n">
-        <v>39.90316605122506</v>
+        <v>196.0000000000003</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -36958,19 +36958,19 @@
         <v>158.5361911433361</v>
       </c>
       <c r="K30" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>44.51793317753517</v>
       </c>
       <c r="M30" t="n">
-        <v>44.51793317753577</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>196</v>
+        <v>196.0000000000003</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>196.0000000000003</v>
       </c>
       <c r="P30" t="n">
         <v>181.0266837599362</v>
@@ -37010,13 +37010,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>57.88619966292134</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
         <v>72.27475335195533</v>
       </c>
       <c r="D31" t="n">
-        <v>59.46378194444452</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>64.01909516304346</v>
@@ -37025,19 +37025,19 @@
         <v>70.61714403225807</v>
       </c>
       <c r="G31" t="n">
-        <v>100.251864863388</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>146.0922050212795</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>196.0000000000003</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>90.83857046115203</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -37064,22 +37064,22 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>136.2390400511193</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>77.84977718107697</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>118.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>97.55635456989245</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>57.53464715053764</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -37116,13 +37116,13 @@
         <v>20.91395857903028</v>
       </c>
       <c r="K32" t="n">
-        <v>196</v>
+        <v>83.86498492462312</v>
       </c>
       <c r="L32" t="n">
-        <v>104.0419296482413</v>
+        <v>104.0419296482412</v>
       </c>
       <c r="M32" t="n">
-        <v>123.7681509758482</v>
+        <v>196.0000000000004</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
@@ -37131,10 +37131,10 @@
         <v>40.83617062691258</v>
       </c>
       <c r="P32" t="n">
-        <v>94.52059825077588</v>
+        <v>196.0000000000004</v>
       </c>
       <c r="Q32" t="n">
-        <v>196</v>
+        <v>134.4237643020001</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37192,25 +37192,25 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>11.7507659163039</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>196</v>
+        <v>196.0000000000004</v>
       </c>
       <c r="M33" t="n">
         <v>176.3300421645043</v>
       </c>
       <c r="N33" t="n">
-        <v>196</v>
+        <v>196.0000000000004</v>
       </c>
       <c r="O33" t="n">
-        <v>196</v>
+        <v>196.0000000000004</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>11.7507659163026</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -37250,7 +37250,7 @@
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>196.0000000000004</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -37262,25 +37262,25 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>70.86292806557748</v>
+        <v>46.77639101320325</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>196</v>
+        <v>196.0000000000004</v>
       </c>
       <c r="L34" t="n">
-        <v>96.42050298976181</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>1.726618105646828</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -37298,13 +37298,13 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>118.7804219364888</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>196</v>
+        <v>196.0000000000004</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -37350,28 +37350,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>188</v>
+        <v>20.91395857903028</v>
       </c>
       <c r="K35" t="n">
-        <v>83.86498492462314</v>
+        <v>83.86498492462312</v>
       </c>
       <c r="L35" t="n">
         <v>104.0419296482412</v>
       </c>
       <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
         <v>188</v>
       </c>
-      <c r="N35" t="n">
-        <v>45.14035695348758</v>
-      </c>
-      <c r="O35" t="n">
-        <v>40.83617062691258</v>
-      </c>
       <c r="P35" t="n">
-        <v>94.52059825077588</v>
+        <v>159.5831672521458</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37432,22 +37432,22 @@
         <v>158.5361911433361</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="L36" t="n">
-        <v>33.53780709620005</v>
+        <v>28.84116550076812</v>
       </c>
       <c r="M36" t="n">
-        <v>176.3300421645043</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>188</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>181.0266837599362</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -37484,7 +37484,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -37496,61 +37496,61 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>162.7149176383412</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
         <v>188</v>
       </c>
-      <c r="G37" t="n">
+      <c r="X37" t="n">
         <v>188</v>
-      </c>
-      <c r="H37" t="n">
-        <v>62.29441464857939</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>188</v>
-      </c>
-      <c r="L37" t="n">
-        <v>100.4205029897618</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
       </c>
       <c r="Y37" t="n">
         <v>0</v>
@@ -37593,22 +37593,22 @@
         <v>83.86498492462312</v>
       </c>
       <c r="L38" t="n">
-        <v>104.0419296482412</v>
+        <v>188</v>
       </c>
       <c r="M38" t="n">
-        <v>24.22639837445737</v>
+        <v>188</v>
       </c>
       <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>75.62509690038701</v>
+      </c>
+      <c r="P38" t="n">
         <v>188</v>
       </c>
-      <c r="O38" t="n">
-        <v>40.83617062691258</v>
-      </c>
-      <c r="P38" t="n">
-        <v>94.52059825077588</v>
-      </c>
       <c r="Q38" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37666,16 +37666,16 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>158.5361911433361</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>4.073998239536125</v>
       </c>
       <c r="L39" t="n">
-        <v>28.84116550076809</v>
+        <v>188</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>176.3300421645043</v>
       </c>
       <c r="N39" t="n">
         <v>188</v>
@@ -37684,7 +37684,7 @@
         <v>188</v>
       </c>
       <c r="P39" t="n">
-        <v>181.0266837599362</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -37724,67 +37724,67 @@
         <v>188</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>162.714917638341</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
         <v>188</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="n">
-        <v>127.5139927120905</v>
-      </c>
-      <c r="L40" t="n">
-        <v>100.4205029897618</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>122.7804219364888</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
@@ -37824,16 +37824,16 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>20.91395857903028</v>
+        <v>188</v>
       </c>
       <c r="K41" t="n">
+        <v>83.86498492462314</v>
+      </c>
+      <c r="L41" t="n">
+        <v>104.0419296482412</v>
+      </c>
+      <c r="M41" t="n">
         <v>188</v>
-      </c>
-      <c r="L41" t="n">
-        <v>188</v>
-      </c>
-      <c r="M41" t="n">
-        <v>24.13331294732171</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -37842,10 +37842,10 @@
         <v>40.83617062691258</v>
       </c>
       <c r="P41" t="n">
-        <v>94.52059825077588</v>
+        <v>139.6609552042635</v>
       </c>
       <c r="Q41" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37906,22 +37906,22 @@
         <v>158.5361911433361</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="L42" t="n">
+        <v>28.84116550076812</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
         <v>188</v>
       </c>
-      <c r="M42" t="n">
-        <v>176.3300421645043</v>
-      </c>
-      <c r="N42" t="n">
-        <v>188</v>
-      </c>
-      <c r="O42" t="n">
-        <v>33.53780709620008</v>
-      </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>181.0266837599362</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -37961,7 +37961,7 @@
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>0.2747533519552948</v>
+        <v>0.2747533519553772</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -38070,10 +38070,10 @@
         <v>104.0419296482412</v>
       </c>
       <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
         <v>155</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>40.83617062691258</v>
@@ -38143,13 +38143,13 @@
         <v>155</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="L45" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
         <v>148.7373737373738</v>
@@ -38158,7 +38158,7 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
